--- a/content/backtrack2abq/data/dance-schedule.xlsx
+++ b/content/backtrack2abq/data/dance-schedule.xlsx
@@ -3,69 +3,678 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25000" windowHeight="10000" firstSheet="0" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Thursday July 1 2027" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Friday July 2 2027" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Saturday July 3 2027" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Sunday July 4 2027" state="visible" r:id="rId7"/>
+    <sheet sheetId="1" name="Thursday July 2" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Friday July 3" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Saturday July 4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="183">
   <si>
     <t>Time</t>
   </si>
   <si>
-    <t>Room TBA</t>
-  </si>
-  <si>
-    <t>7:00p-10:00p</t>
-  </si>
-  <si>
-    <t>Various : Trail-In Dance - Justin Russell &amp; Tony Oxendine</t>
-  </si>
-  <si>
-    <t>9:30a-11:30a</t>
-  </si>
-  <si>
-    <t>* Refresher (room &amp; caller assignments TBA)</t>
-  </si>
-  <si>
-    <t>3:00p-5:00p</t>
-  </si>
-  <si>
-    <t>* Dancing — all levels (room &amp; caller assignments TBA)</t>
-  </si>
-  <si>
-    <t>10:00a-12:00p</t>
-  </si>
-  <si>
-    <t>1:00p-4:00p</t>
-  </si>
-  <si>
-    <t>8:00p-10:00p</t>
-  </si>
-  <si>
-    <t>* Dancing (room &amp; caller assignments TBA)</t>
-  </si>
-  <si>
-    <t>12:00p-5:00p</t>
+    <t>Ballroom Centre</t>
+  </si>
+  <si>
+    <t>Ballroom East</t>
+  </si>
+  <si>
+    <t>Ballroom West</t>
+  </si>
+  <si>
+    <t>Drummond Ballroom</t>
+  </si>
+  <si>
+    <t>Hemon</t>
+  </si>
+  <si>
+    <t>Jarry/Joyce</t>
+  </si>
+  <si>
+    <t>Kafka/Lamartine</t>
+  </si>
+  <si>
+    <t>Salon 6/7</t>
+  </si>
+  <si>
+    <t>Salon A-C</t>
+  </si>
+  <si>
+    <t>12:30p-1:30p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Kris Jensen
+GCA: Tim Stephens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3B : Dancing - Barry Clasper
+GCA: Osamu Miyabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Justin Russell
+GCA: Patrick Aubert</t>
+  </si>
+  <si>
+    <t>C1 &amp; C2 : Dancing - Vic Ceder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1 : Dancing - Michael Kellogg
+GCA: Andy Chong</t>
+  </si>
+  <si>
+    <t>1:30p-2:30p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2 : Dancing - Don Moger
+GCA: Jenn Engimann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2 : Dancing - Rob French
+GCA: Michael Maltenfort</t>
+  </si>
+  <si>
+    <t>SSD : Skirt Work Hour - Wendy VanderMeulen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Michael Kellogg
+GCA: Michael Levy</t>
+  </si>
+  <si>
+    <t>SSD : Dancing - Ted Lizotte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3A : Dancing - Sandie Bryant
+GCA: Jane Clewe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Kris Jensen
+GCA: Fen Tamanaha</t>
+  </si>
+  <si>
+    <t>2:30p-3:30p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1 : Dancing - Ted Lizotte
+GCA: Terri Sherrer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2 : Dancing - Kris Jensen
+GCA: Andy Chong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Wendy VanderMeulen
+GCA: Karla Westphal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Michael Kellogg
+GCA: John Ryan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3B : Dancing - Rob French
+GCA: John Hawley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Don Moger
+GCA: Rick Hawes</t>
+  </si>
+  <si>
+    <t>3:30p-4:30p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2 : Dancing - Rob French
+GCA: Michael Maltenfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2 : Dancing - Sandie Bryant
+GCA: Dave Decot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Justin Russell
+GCA: Mary Thurston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Wendy VanderMeulen
+GCA: Tim Stephens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C4 : Dancing - Vic Ceder
+GCA: John Ryan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3A : Dancing - Vic Ceder
+GCA: Jenn Engimann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Barry Clasper
+GCA: Jane Clewe</t>
   </si>
   <si>
     <t>7:00p-8:00p</t>
   </si>
   <si>
-    <t>* All-Together Dance (room &amp; caller assignments TBA)</t>
+    <t xml:space="preserve">A2 : Dancing - Ted Lizotte
+GCA: Rick Hawes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2 : Dancing - Rob French
+GCA: Kent Forrester</t>
+  </si>
+  <si>
+    <t>SSD : Leather Tip - Michael Kellogg &amp; Terri Sherrer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Don Moger
+GCA: David Hartman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Justin Russell
+GCA: Mike Neiheisel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3A : Dancing - Vic Ceder
+GCA: John Hawley</t>
+  </si>
+  <si>
+    <t>Various : Zoom Reunion Hour - Ett McAtee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Sandie Bryant
+GCA: Osamu Miyabe</t>
+  </si>
+  <si>
+    <t>8:00p-9:00p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1 : Dancing - Kris Jensen
+GCA: Karla Westphal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2 : Dancing - Don Moger
+GCA: John Hawley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Justin Russell
+GCA: Janienne A-K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Vic Ceder
+GCA: Rick Hawes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3B : Dancing - Sandie Bryant
+GCA: Michael Maltenfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Ted Lizotte
+GCA: Brian Jarvis</t>
+  </si>
+  <si>
+    <t>9:00p-10:00p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2 : Dancing - Justin Russell
+GCA: David Hartman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2 : Dancing - Barry Clasper
+GCA: Jane Clewe</t>
+  </si>
+  <si>
+    <t>SSD : Glowstick Hour - Dave Hutchinson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Ted Lizotte
+GCA: Mary Thurston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Kris Jensen
+GCA: Patti Cummings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C4 : Dancing - Rob French
+GCA: Bill van Melle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Michael Kellogg
+GCA: Michel Maltenfort</t>
+  </si>
+  <si>
+    <t>10:00p-11:00p</t>
+  </si>
+  <si>
+    <t>SSD : Zombie Callers - Various</t>
+  </si>
+  <si>
+    <t>10:15a-11:00a</t>
+  </si>
+  <si>
+    <t>SSD : All Callers Dance - All Callers</t>
+  </si>
+  <si>
+    <t>"</t>
+  </si>
+  <si>
+    <t>11:00a-12:00p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Sandie Bryant
+GCA: Michael Levy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Ted Lizotte
+GCA: Karla Westphal</t>
+  </si>
+  <si>
+    <t>C3A : Dancing - Don Moger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Dayle Hodge
+GCA: Tim Stephens</t>
+  </si>
+  <si>
+    <t>C2 : Dancing - Michael Kellogg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2 : Dancing - Justin Russell
+GCA: Osamu Miyabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2 : Dancing - Ted Lizotte
+GCA: Dave Decot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2 : Dancing - Vic Ceder
+GCA: Terri Sherrer</t>
+  </si>
+  <si>
+    <t>SSD : Women's Tip - Jenn Engimann &amp; Marge Coahran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Kris Jensen
+GCA: David Hartman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Don Moger
+GCA: J.M. Robichaud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3A : Dancing - Sandie Bryant
+GCA: Osamu Miyabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Michael Kellogg
+GCA: Kent Forrester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1 : Dancing - Justin Russell
+GCA: Osamu Miyabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2 : Dancing - Barry Clasper
+GCA: John Hawley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Ted Lizotte
+GCA: Allan Hurst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Michael Kellogg
+GCA: Kurt Gollhardt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3B : Dancing - Vic Ceder
+GCA: Harlan Kerr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Rob French
+GCA: Bill van Melle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2 : Dancing - Sandie Bryant
+GCA: Harlan Kerr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2 : Dancing - Don Moger
+GCA: Andy Chong</t>
+  </si>
+  <si>
+    <t>SSD : Bear Tip - Kurt Gollhardt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Michael Kellogg
+GCA: Jenn Engimann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Kris Jensen
+GCA: Allan Hurst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C4 : Dancing - Rob French
+GCA: Jane Clewe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Ted Lizotte
+GCA: Dave Decot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2 : Intro to C1 - Vic Ceder
+GCA: David Hartman</t>
+  </si>
+  <si>
+    <t>C2 : Dancing - Sandie Bryant</t>
+  </si>
+  <si>
+    <t>Intro : Intro to Square Dancing - Don Moger</t>
+  </si>
+  <si>
+    <t>Plus : Intro to A1 - Rick Hawes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Dave Hutchinson
+GCA: Greg Moore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3A : Dancing - Rob French
+GCA: Jane Clewe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Kris Jensen
+GCA: Andy Chong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1 : Dancing - Barry Clasper
+GCA: Karla Westphal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2 : Dancing - Michael Kellogg
+GCA: Osamu Miyabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Justin Russell
+GCA: Tim Stephens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Intro to Plus - Ted Lizotte
+GCA: Patrick Aubert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3B : Dancing - Sandie Bryant
+GCA: Bill van Melle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Rob French
+GCA: Jenn Engimann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2 : Dancing - Michael Kellogg
+GCA: Kurt Gollhardt</t>
+  </si>
+  <si>
+    <t>C2 : Dancing - Kris Jensen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Sandie Bryant
+GCA: Mike Neiheisel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Justin Russell
+GCA: Greg Moore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C4 : Dancing - Barry Clasper
+GCA: Harlan Kerr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Vic Ceder
+GCA: Rick Hawes</t>
+  </si>
+  <si>
+    <t>SSD : Moonshine Tip - Dayle Hodge &amp; Karla Westphal</t>
+  </si>
+  <si>
+    <t>12:00p-1:30p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* Lunch Break
+ROOMS: NONE</t>
+  </si>
+  <si>
+    <t>9:00a-10:00a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2 : Dancing - Michael Kellogg
+GCA: Karla Westphal</t>
+  </si>
+  <si>
+    <t>C2 : Dancing - Rob French</t>
+  </si>
+  <si>
+    <t>A1/A2 : Advanced Hothash - Justin Russell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Vic Ceder
+GCA: David Hartman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Kris Jensen
+GCA: Karin Rabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3A : Dancing - Barry Clasper
+GCA: Michael Maltenfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Ted Lizotte
+GCA: Kent Forrester</t>
+  </si>
+  <si>
+    <t>10:00a-11:00a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2 : Dancing - Barry Clasper
+GCA: Dave Decot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2 : Dancing - Kris Jensen
+GCA: Osamu Miyabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Plus TNP - Ted Lizotte
+GCA: Michael Levy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Justin Russell
+GCA: Michael Maltenfort</t>
+  </si>
+  <si>
+    <t>* Intro to calling - Bill Eyler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Vic Ceder
+GCA: Kent Forrester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3B : Dancing - Rob French
+GCA: Ryo Sasaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Don Moger
+GCA: Harlan Kerr</t>
+  </si>
+  <si>
+    <t>A1 : Dancing - Ted Lizotte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2 : Dancing - Vic Ceder
+GCA: Fen Tamanaha</t>
+  </si>
+  <si>
+    <t>SSD : Kilt Tip - Brian Crawford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Don Moger
+GCA: Karin Rabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Allan Hurst
+GCA: Patrick Aubert</t>
+  </si>
+  <si>
+    <t>C4 : Dancing - Sandie Bryant</t>
+  </si>
+  <si>
+    <t>C2 : Dancing - Dave Hutchinson</t>
+  </si>
+  <si>
+    <t>A2 : Dancing - Kris Jensen</t>
+  </si>
+  <si>
+    <t>2:00p-3:00p</t>
+  </si>
+  <si>
+    <t>Plus : Dancing - Sandie Bryant</t>
+  </si>
+  <si>
+    <t>C3A : Dancing - Michael Kellogg</t>
+  </si>
+  <si>
+    <t>C1 : Dancing - Dayle Hodge</t>
+  </si>
+  <si>
+    <t>C2 : Dancing - Dayle Hodge</t>
+  </si>
+  <si>
+    <t>3:00p-4:00p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Brian Crawford
+GCA: Rick Hawes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3B : Dancing - Barry Clasper
+GCA: Harlan Kerr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Michael Kellogg
+GCA: Patti Cummings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Rob French
+GCA: Osamu Miyabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2 : Dancing - Dayle Hodge
+GCA: Bill van Melle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Sandie Bryant
+GCA: David Hartman</t>
+  </si>
+  <si>
+    <t>4:00p-5:00p</t>
+  </si>
+  <si>
+    <t>C4 : Dancing - Vic Ceder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Justin Russell
+GCA: Brian Jarvis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 &amp; C2 : Dancing - Kris Jensen
+GCA: Jenn Engimann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Dayle Hodge
+GCA: Michael Maltenfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2 : Dancing - Sandie Bryant
+GCA: David Hartman</t>
+  </si>
+  <si>
+    <t>8:00p-8:30p</t>
+  </si>
+  <si>
+    <t>Plus : Medallion Tip - Vic Ceder</t>
+  </si>
+  <si>
+    <t>SSD : GCA Caller Showcase Dance - Janienne Alexander</t>
+  </si>
+  <si>
+    <t>C1 : GCA Caller Showcase Dance - Bill van Melle</t>
+  </si>
+  <si>
+    <t>A1/A2 : GCA Caller Showcase Dance - David Hartman</t>
+  </si>
+  <si>
+    <t>Plus : GCA Caller Showcase Dance - Michael Levy</t>
+  </si>
+  <si>
+    <t>8:30p-9:00p</t>
+  </si>
+  <si>
+    <t>SSD : GCA Caller Showcase Dance - Brian Jarvis</t>
+  </si>
+  <si>
+    <t>C1 &amp; C2 : GCA Caller Showcase Dance - John Hawley</t>
+  </si>
+  <si>
+    <t>A1/A2 : GCA Caller Showcase Dance - Michael Maltenfort</t>
+  </si>
+  <si>
+    <t>Plus : GCA Caller Showcase Dance - Rick Hawes</t>
+  </si>
+  <si>
+    <t>9:00p-9:30p</t>
+  </si>
+  <si>
+    <t>* Country Western Dance - until 1am</t>
+  </si>
+  <si>
+    <t>SSD : GCA Caller Showcase Dance - Tim Stephens</t>
+  </si>
+  <si>
+    <t>C1 : GCA Caller Showcase Dance - Ryo Sasaki</t>
+  </si>
+  <si>
+    <t>A1/A2 : GCA Caller Showcase Dance - Allan Hurst</t>
+  </si>
+  <si>
+    <t>Plus : GCA Caller Showcase Dance - Karla Westphal</t>
+  </si>
+  <si>
+    <t>9:30p-10:00p</t>
+  </si>
+  <si>
+    <t>SSD : GCA Caller Showcase Dance - Patrick Aubert</t>
+  </si>
+  <si>
+    <t>C3A : GCA Caller Showcase Dance - Jane Clewe</t>
+  </si>
+  <si>
+    <t>A1/A2 : GCA Caller Showcase Dance - Kurt Gollhardt</t>
+  </si>
+  <si>
+    <t>Plus : GCA Caller Showcase Dance - Karin Rabe &amp; Greg Moore</t>
+  </si>
+  <si>
+    <t>12:00p-2:00p</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -73,16 +682,40 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill/>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -90,12 +723,45 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B7B7B7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B7B7B7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B7B7B7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B7B7B7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -188,7 +854,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -223,7 +888,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -258,16 +922,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -389,194 +1057,840 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="10" width="26" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="9" width="26" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
+      <c r="I1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+    </row>
+    <row r="3" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+    </row>
+    <row r="11" ht="48" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="10" width="26" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>11</v>
+    </row>
+    <row r="2" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="J5" s="4"/>
+    </row>
+    <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/content/backtrack2abq/data/dance-schedule.xlsx
+++ b/content/backtrack2abq/data/dance-schedule.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10726"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16E6C9D-744A-A144-BEEF-F54B2BECA524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25000" windowHeight="10000" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="34900" windowHeight="19580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Thursday July 2" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Friday July 3" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Saturday July 4" state="visible" r:id="rId6"/>
+    <sheet name="Thursday July 2" sheetId="1" r:id="rId1"/>
+    <sheet name="Friday July 3" sheetId="2" r:id="rId2"/>
+    <sheet name="Saturday July 4" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="187">
   <si>
     <t>Time</t>
   </si>
@@ -51,199 +52,199 @@
     <t>12:30p-1:30p</t>
   </si>
   <si>
-    <t xml:space="preserve">Plus : Dancing - Kris Jensen
+    <t>Plus : Dancing - Kris Jensen
 GCA: Tim Stephens</t>
   </si>
   <si>
-    <t xml:space="preserve">C3B : Dancing - Barry Clasper
+    <t>C3B : Dancing - Barry Clasper
 GCA: Osamu Miyabe</t>
   </si>
   <si>
-    <t xml:space="preserve">SSD : Dancing - Justin Russell
+    <t>SSD : Dancing - Justin Russell
 GCA: Patrick Aubert</t>
   </si>
   <si>
     <t>C1 &amp; C2 : Dancing - Vic Ceder</t>
   </si>
   <si>
-    <t xml:space="preserve">A1 : Dancing - Michael Kellogg
+    <t>A1 : Dancing - Michael Kellogg
 GCA: Andy Chong</t>
   </si>
   <si>
     <t>1:30p-2:30p</t>
   </si>
   <si>
-    <t xml:space="preserve">A2 : Dancing - Don Moger
+    <t>A2 : Dancing - Don Moger
 GCA: Jenn Engimann</t>
   </si>
   <si>
-    <t xml:space="preserve">C2 : Dancing - Rob French
+    <t>C2 : Dancing - Rob French
 GCA: Michael Maltenfort</t>
   </si>
   <si>
     <t>SSD : Skirt Work Hour - Wendy VanderMeulen</t>
   </si>
   <si>
-    <t xml:space="preserve">Plus : Dancing - Michael Kellogg
+    <t>Plus : Dancing - Michael Kellogg
 GCA: Michael Levy</t>
   </si>
   <si>
     <t>SSD : Dancing - Ted Lizotte</t>
   </si>
   <si>
-    <t xml:space="preserve">C3A : Dancing - Sandie Bryant
+    <t>C3A : Dancing - Sandie Bryant
 GCA: Jane Clewe</t>
   </si>
   <si>
-    <t xml:space="preserve">C1 : Dancing - Kris Jensen
+    <t>C1 : Dancing - Kris Jensen
 GCA: Fen Tamanaha</t>
   </si>
   <si>
     <t>2:30p-3:30p</t>
   </si>
   <si>
-    <t xml:space="preserve">A1 : Dancing - Ted Lizotte
+    <t>A1 : Dancing - Ted Lizotte
 GCA: Terri Sherrer</t>
   </si>
   <si>
-    <t xml:space="preserve">C2 : Dancing - Kris Jensen
+    <t>C2 : Dancing - Kris Jensen
 GCA: Andy Chong</t>
   </si>
   <si>
-    <t xml:space="preserve">Plus : Dancing - Wendy VanderMeulen
+    <t>Plus : Dancing - Wendy VanderMeulen
 GCA: Karla Westphal</t>
   </si>
   <si>
-    <t xml:space="preserve">SSD : Dancing - Michael Kellogg
+    <t>SSD : Dancing - Michael Kellogg
 GCA: John Ryan</t>
   </si>
   <si>
-    <t xml:space="preserve">C3B : Dancing - Rob French
+    <t>C3B : Dancing - Rob French
 GCA: John Hawley</t>
   </si>
   <si>
-    <t xml:space="preserve">C1 : Dancing - Don Moger
+    <t>C1 : Dancing - Don Moger
 GCA: Rick Hawes</t>
   </si>
   <si>
     <t>3:30p-4:30p</t>
   </si>
   <si>
-    <t xml:space="preserve">A2 : Dancing - Rob French
+    <t>A2 : Dancing - Rob French
 GCA: Michael Maltenfort</t>
   </si>
   <si>
-    <t xml:space="preserve">C2 : Dancing - Sandie Bryant
+    <t>C2 : Dancing - Sandie Bryant
 GCA: Dave Decot</t>
   </si>
   <si>
-    <t xml:space="preserve">Plus : Dancing - Justin Russell
+    <t>Plus : Dancing - Justin Russell
 GCA: Mary Thurston</t>
   </si>
   <si>
-    <t xml:space="preserve">SSD : Dancing - Wendy VanderMeulen
+    <t>SSD : Dancing - Wendy VanderMeulen
 GCA: Tim Stephens</t>
   </si>
   <si>
-    <t xml:space="preserve">C4 : Dancing - Vic Ceder
+    <t>C4 : Dancing - Vic Ceder
 GCA: John Ryan</t>
   </si>
   <si>
-    <t xml:space="preserve">C3A : Dancing - Vic Ceder
+    <t>C3A : Dancing - Vic Ceder
 GCA: Jenn Engimann</t>
   </si>
   <si>
-    <t xml:space="preserve">C1 : Dancing - Barry Clasper
+    <t>C1 : Dancing - Barry Clasper
 GCA: Jane Clewe</t>
   </si>
   <si>
     <t>7:00p-8:00p</t>
   </si>
   <si>
-    <t xml:space="preserve">A2 : Dancing - Ted Lizotte
+    <t>A2 : Dancing - Ted Lizotte
 GCA: Rick Hawes</t>
   </si>
   <si>
-    <t xml:space="preserve">C2 : Dancing - Rob French
+    <t>C2 : Dancing - Rob French
 GCA: Kent Forrester</t>
   </si>
   <si>
     <t>SSD : Leather Tip - Michael Kellogg &amp; Terri Sherrer</t>
   </si>
   <si>
-    <t xml:space="preserve">Plus : Dancing - Don Moger
+    <t>Plus : Dancing - Don Moger
 GCA: David Hartman</t>
   </si>
   <si>
-    <t xml:space="preserve">SSD : Dancing - Justin Russell
+    <t>SSD : Dancing - Justin Russell
 GCA: Mike Neiheisel</t>
   </si>
   <si>
-    <t xml:space="preserve">C3A : Dancing - Vic Ceder
+    <t>C3A : Dancing - Vic Ceder
 GCA: John Hawley</t>
   </si>
   <si>
     <t>Various : Zoom Reunion Hour - Ett McAtee</t>
   </si>
   <si>
-    <t xml:space="preserve">C1 : Dancing - Sandie Bryant
+    <t>C1 : Dancing - Sandie Bryant
 GCA: Osamu Miyabe</t>
   </si>
   <si>
     <t>8:00p-9:00p</t>
   </si>
   <si>
-    <t xml:space="preserve">A1 : Dancing - Kris Jensen
+    <t>A1 : Dancing - Kris Jensen
 GCA: Karla Westphal</t>
   </si>
   <si>
-    <t xml:space="preserve">C2 : Dancing - Don Moger
+    <t>C2 : Dancing - Don Moger
 GCA: John Hawley</t>
   </si>
   <si>
-    <t xml:space="preserve">Plus : Dancing - Justin Russell
+    <t>Plus : Dancing - Justin Russell
 GCA: Janienne A-K</t>
   </si>
   <si>
-    <t xml:space="preserve">SSD : Dancing - Vic Ceder
+    <t>SSD : Dancing - Vic Ceder
 GCA: Rick Hawes</t>
   </si>
   <si>
-    <t xml:space="preserve">C3B : Dancing - Sandie Bryant
+    <t>C3B : Dancing - Sandie Bryant
 GCA: Michael Maltenfort</t>
   </si>
   <si>
-    <t xml:space="preserve">C1 : Dancing - Ted Lizotte
+    <t>C1 : Dancing - Ted Lizotte
 GCA: Brian Jarvis</t>
   </si>
   <si>
     <t>9:00p-10:00p</t>
   </si>
   <si>
-    <t xml:space="preserve">A2 : Dancing - Justin Russell
+    <t>A2 : Dancing - Justin Russell
 GCA: David Hartman</t>
   </si>
   <si>
-    <t xml:space="preserve">C2 : Dancing - Barry Clasper
+    <t>C2 : Dancing - Barry Clasper
 GCA: Jane Clewe</t>
   </si>
   <si>
     <t>SSD : Glowstick Hour - Dave Hutchinson</t>
   </si>
   <si>
-    <t xml:space="preserve">Plus : Dancing - Ted Lizotte
+    <t>Plus : Dancing - Ted Lizotte
 GCA: Mary Thurston</t>
   </si>
   <si>
-    <t xml:space="preserve">SSD : Dancing - Kris Jensen
+    <t>SSD : Dancing - Kris Jensen
 GCA: Patti Cummings</t>
   </si>
   <si>
-    <t xml:space="preserve">C4 : Dancing - Rob French
+    <t>C4 : Dancing - Rob French
 GCA: Bill van Melle</t>
   </si>
   <si>
-    <t xml:space="preserve">C1 : Dancing - Michael Kellogg
+    <t>C1 : Dancing - Michael Kellogg
 GCA: Michel Maltenfort</t>
   </si>
   <si>
@@ -265,107 +266,107 @@
     <t>11:00a-12:00p</t>
   </si>
   <si>
-    <t xml:space="preserve">C1 : Dancing - Sandie Bryant
+    <t>C1 : Dancing - Sandie Bryant
 GCA: Michael Levy</t>
   </si>
   <si>
-    <t xml:space="preserve">Plus : Dancing - Ted Lizotte
+    <t>Plus : Dancing - Ted Lizotte
 GCA: Karla Westphal</t>
   </si>
   <si>
     <t>C3A : Dancing - Don Moger</t>
   </si>
   <si>
-    <t xml:space="preserve">SSD : Dancing - Dayle Hodge
+    <t>SSD : Dancing - Dayle Hodge
 GCA: Tim Stephens</t>
   </si>
   <si>
     <t>C2 : Dancing - Michael Kellogg</t>
   </si>
   <si>
-    <t xml:space="preserve">A2 : Dancing - Justin Russell
+    <t>A2 : Dancing - Justin Russell
 GCA: Osamu Miyabe</t>
   </si>
   <si>
-    <t xml:space="preserve">A2 : Dancing - Ted Lizotte
+    <t>A2 : Dancing - Ted Lizotte
 GCA: Dave Decot</t>
   </si>
   <si>
-    <t xml:space="preserve">C2 : Dancing - Vic Ceder
+    <t>C2 : Dancing - Vic Ceder
 GCA: Terri Sherrer</t>
   </si>
   <si>
     <t>SSD : Women's Tip - Jenn Engimann &amp; Marge Coahran</t>
   </si>
   <si>
-    <t xml:space="preserve">Plus : Dancing - Kris Jensen
+    <t>Plus : Dancing - Kris Jensen
 GCA: David Hartman</t>
   </si>
   <si>
-    <t xml:space="preserve">SSD : Dancing - Don Moger
+    <t>SSD : Dancing - Don Moger
 GCA: J.M. Robichaud</t>
   </si>
   <si>
-    <t xml:space="preserve">C3A : Dancing - Sandie Bryant
+    <t>C3A : Dancing - Sandie Bryant
 GCA: Osamu Miyabe</t>
   </si>
   <si>
-    <t xml:space="preserve">C1 : Dancing - Michael Kellogg
+    <t>C1 : Dancing - Michael Kellogg
 GCA: Kent Forrester</t>
   </si>
   <si>
-    <t xml:space="preserve">A1 : Dancing - Justin Russell
+    <t>A1 : Dancing - Justin Russell
 GCA: Osamu Miyabe</t>
   </si>
   <si>
-    <t xml:space="preserve">C2 : Dancing - Barry Clasper
+    <t>C2 : Dancing - Barry Clasper
 GCA: John Hawley</t>
   </si>
   <si>
-    <t xml:space="preserve">Plus : Dancing - Ted Lizotte
+    <t>Plus : Dancing - Ted Lizotte
 GCA: Allan Hurst</t>
   </si>
   <si>
-    <t xml:space="preserve">SSD : Dancing - Michael Kellogg
+    <t>SSD : Dancing - Michael Kellogg
 GCA: Kurt Gollhardt</t>
   </si>
   <si>
-    <t xml:space="preserve">C3B : Dancing - Vic Ceder
+    <t>C3B : Dancing - Vic Ceder
 GCA: Harlan Kerr</t>
   </si>
   <si>
-    <t xml:space="preserve">C1 : Dancing - Rob French
+    <t>C1 : Dancing - Rob French
 GCA: Bill van Melle</t>
   </si>
   <si>
-    <t xml:space="preserve">A2 : Dancing - Sandie Bryant
+    <t>A2 : Dancing - Sandie Bryant
 GCA: Harlan Kerr</t>
   </si>
   <si>
-    <t xml:space="preserve">C2 : Dancing - Don Moger
+    <t>C2 : Dancing - Don Moger
 GCA: Andy Chong</t>
   </si>
   <si>
     <t>SSD : Bear Tip - Kurt Gollhardt</t>
   </si>
   <si>
-    <t xml:space="preserve">Plus : Dancing - Michael Kellogg
+    <t>Plus : Dancing - Michael Kellogg
 GCA: Jenn Engimann</t>
   </si>
   <si>
-    <t xml:space="preserve">SSD : Dancing - Kris Jensen
+    <t>SSD : Dancing - Kris Jensen
 GCA: Allan Hurst</t>
   </si>
   <si>
-    <t xml:space="preserve">C4 : Dancing - Rob French
+    <t>C4 : Dancing - Rob French
 GCA: Jane Clewe</t>
   </si>
   <si>
-    <t xml:space="preserve">C1 : Dancing - Ted Lizotte
+    <t>C1 : Dancing - Ted Lizotte
 GCA: Dave Decot</t>
   </si>
   <si>
-    <t xml:space="preserve">A2 : Intro to C1 - Vic Ceder
+    <t>A2 : Intro to C1 - Vic Ceder
 GCA: David Hartman</t>
   </si>
   <si>
@@ -378,62 +379,62 @@
     <t>Plus : Intro to A1 - Rick Hawes</t>
   </si>
   <si>
-    <t xml:space="preserve">SSD : Dancing - Dave Hutchinson
+    <t>SSD : Dancing - Dave Hutchinson
 GCA: Greg Moore</t>
   </si>
   <si>
-    <t xml:space="preserve">C3A : Dancing - Rob French
+    <t>C3A : Dancing - Rob French
 GCA: Jane Clewe</t>
   </si>
   <si>
-    <t xml:space="preserve">C1 : Dancing - Kris Jensen
+    <t>C1 : Dancing - Kris Jensen
 GCA: Andy Chong</t>
   </si>
   <si>
-    <t xml:space="preserve">A1 : Dancing - Barry Clasper
+    <t>A1 : Dancing - Barry Clasper
 GCA: Karla Westphal</t>
   </si>
   <si>
-    <t xml:space="preserve">C2 : Dancing - Michael Kellogg
+    <t>C2 : Dancing - Michael Kellogg
 GCA: Osamu Miyabe</t>
   </si>
   <si>
-    <t xml:space="preserve">Plus : Dancing - Justin Russell
+    <t>Plus : Dancing - Justin Russell
 GCA: Tim Stephens</t>
   </si>
   <si>
-    <t xml:space="preserve">SSD : Intro to Plus - Ted Lizotte
+    <t>SSD : Intro to Plus - Ted Lizotte
 GCA: Patrick Aubert</t>
   </si>
   <si>
-    <t xml:space="preserve">C3B : Dancing - Sandie Bryant
+    <t>C3B : Dancing - Sandie Bryant
 GCA: Bill van Melle</t>
   </si>
   <si>
-    <t xml:space="preserve">C1 : Dancing - Rob French
+    <t>C1 : Dancing - Rob French
 GCA: Jenn Engimann</t>
   </si>
   <si>
-    <t xml:space="preserve">A2 : Dancing - Michael Kellogg
+    <t>A2 : Dancing - Michael Kellogg
 GCA: Kurt Gollhardt</t>
   </si>
   <si>
     <t>C2 : Dancing - Kris Jensen</t>
   </si>
   <si>
-    <t xml:space="preserve">Plus : Dancing - Sandie Bryant
+    <t>Plus : Dancing - Sandie Bryant
 GCA: Mike Neiheisel</t>
   </si>
   <si>
-    <t xml:space="preserve">SSD : Dancing - Justin Russell
+    <t>SSD : Dancing - Justin Russell
 GCA: Greg Moore</t>
   </si>
   <si>
-    <t xml:space="preserve">C4 : Dancing - Barry Clasper
+    <t>C4 : Dancing - Barry Clasper
 GCA: Harlan Kerr</t>
   </si>
   <si>
-    <t xml:space="preserve">C1 : Dancing - Vic Ceder
+    <t>C1 : Dancing - Vic Ceder
 GCA: Rick Hawes</t>
   </si>
   <si>
@@ -443,14 +444,14 @@
     <t>12:00p-1:30p</t>
   </si>
   <si>
-    <t xml:space="preserve">* Lunch Break
+    <t>* Lunch Break
 ROOMS: NONE</t>
   </si>
   <si>
     <t>9:00a-10:00a</t>
   </si>
   <si>
-    <t xml:space="preserve">A2 : Dancing - Michael Kellogg
+    <t>A2 : Dancing - Michael Kellogg
 GCA: Karla Westphal</t>
   </si>
   <si>
@@ -460,71 +461,71 @@
     <t>A1/A2 : Advanced Hothash - Justin Russell</t>
   </si>
   <si>
-    <t xml:space="preserve">Plus : Dancing - Vic Ceder
+    <t>Plus : Dancing - Vic Ceder
 GCA: David Hartman</t>
   </si>
   <si>
-    <t xml:space="preserve">SSD : Dancing - Kris Jensen
+    <t>SSD : Dancing - Kris Jensen
 GCA: Karin Rabe</t>
   </si>
   <si>
-    <t xml:space="preserve">C3A : Dancing - Barry Clasper
+    <t>C3A : Dancing - Barry Clasper
 GCA: Michael Maltenfort</t>
   </si>
   <si>
-    <t xml:space="preserve">C1 : Dancing - Ted Lizotte
+    <t>C1 : Dancing - Ted Lizotte
 GCA: Kent Forrester</t>
   </si>
   <si>
     <t>10:00a-11:00a</t>
   </si>
   <si>
-    <t xml:space="preserve">A2 : Dancing - Barry Clasper
+    <t>A2 : Dancing - Barry Clasper
 GCA: Dave Decot</t>
   </si>
   <si>
-    <t xml:space="preserve">C2 : Dancing - Kris Jensen
+    <t>C2 : Dancing - Kris Jensen
 GCA: Osamu Miyabe</t>
   </si>
   <si>
-    <t xml:space="preserve">Plus : Plus TNP - Ted Lizotte
+    <t>Plus : Plus TNP - Ted Lizotte
 GCA: Michael Levy</t>
   </si>
   <si>
-    <t xml:space="preserve">Plus : Dancing - Justin Russell
+    <t>Plus : Dancing - Justin Russell
 GCA: Michael Maltenfort</t>
   </si>
   <si>
     <t>* Intro to calling - Bill Eyler</t>
   </si>
   <si>
-    <t xml:space="preserve">SSD : Dancing - Vic Ceder
+    <t>SSD : Dancing - Vic Ceder
 GCA: Kent Forrester</t>
   </si>
   <si>
-    <t xml:space="preserve">C3B : Dancing - Rob French
+    <t>C3B : Dancing - Rob French
 GCA: Ryo Sasaki</t>
   </si>
   <si>
-    <t xml:space="preserve">C1 : Dancing - Don Moger
+    <t>C1 : Dancing - Don Moger
 GCA: Harlan Kerr</t>
   </si>
   <si>
     <t>A1 : Dancing - Ted Lizotte</t>
   </si>
   <si>
-    <t xml:space="preserve">C2 : Dancing - Vic Ceder
+    <t>C2 : Dancing - Vic Ceder
 GCA: Fen Tamanaha</t>
   </si>
   <si>
     <t>SSD : Kilt Tip - Brian Crawford</t>
   </si>
   <si>
-    <t xml:space="preserve">Plus : Dancing - Don Moger
+    <t>Plus : Dancing - Don Moger
 GCA: Karin Rabe</t>
   </si>
   <si>
-    <t xml:space="preserve">SSD : Dancing - Allan Hurst
+    <t>SSD : Dancing - Allan Hurst
 GCA: Patrick Aubert</t>
   </si>
   <si>
@@ -555,27 +556,27 @@
     <t>3:00p-4:00p</t>
   </si>
   <si>
-    <t xml:space="preserve">Plus : Dancing - Brian Crawford
+    <t>Plus : Dancing - Brian Crawford
 GCA: Rick Hawes</t>
   </si>
   <si>
-    <t xml:space="preserve">C3B : Dancing - Barry Clasper
+    <t>C3B : Dancing - Barry Clasper
 GCA: Harlan Kerr</t>
   </si>
   <si>
-    <t xml:space="preserve">SSD : Dancing - Michael Kellogg
+    <t>SSD : Dancing - Michael Kellogg
 GCA: Patti Cummings</t>
   </si>
   <si>
-    <t xml:space="preserve">C1 : Dancing - Rob French
+    <t>C1 : Dancing - Rob French
 GCA: Osamu Miyabe</t>
   </si>
   <si>
-    <t xml:space="preserve">C2 : Dancing - Dayle Hodge
+    <t>C2 : Dancing - Dayle Hodge
 GCA: Bill van Melle</t>
   </si>
   <si>
-    <t xml:space="preserve">Plus : Dancing - Sandie Bryant
+    <t>Plus : Dancing - Sandie Bryant
 GCA: David Hartman</t>
   </si>
   <si>
@@ -585,19 +586,19 @@
     <t>C4 : Dancing - Vic Ceder</t>
   </si>
   <si>
-    <t xml:space="preserve">SSD : Dancing - Justin Russell
+    <t>SSD : Dancing - Justin Russell
 GCA: Brian Jarvis</t>
   </si>
   <si>
-    <t xml:space="preserve">C1 &amp; C2 : Dancing - Kris Jensen
+    <t>C1 &amp; C2 : Dancing - Kris Jensen
 GCA: Jenn Engimann</t>
   </si>
   <si>
-    <t xml:space="preserve">Plus : Dancing - Dayle Hodge
+    <t>Plus : Dancing - Dayle Hodge
 GCA: Michael Maltenfort</t>
   </si>
   <si>
-    <t xml:space="preserve">A2 : Dancing - Sandie Bryant
+    <t>A2 : Dancing - Sandie Bryant
 GCA: David Hartman</t>
   </si>
   <si>
@@ -668,34 +669,57 @@
   </si>
   <si>
     <t>12:00p-2:00p</t>
+  </si>
+  <si>
+    <t>4:30p-7:00p</t>
+  </si>
+  <si>
+    <t>* Dinner Break
+ROOMS: NONE</t>
+  </si>
+  <si>
+    <t>8:30-10:00a</t>
+  </si>
+  <si>
+    <t>* Brunch</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="00FFFFFF"/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -707,12 +731,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-        <bgColor rgb="001F4E78"/>
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="2">
@@ -725,16 +749,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B7B7B7"/>
+        <color rgb="FFB7B7B7"/>
       </left>
       <right style="thin">
-        <color rgb="00B7B7B7"/>
+        <color rgb="FFB7B7B7"/>
       </right>
       <top style="thin">
-        <color rgb="00B7B7B7"/>
+        <color rgb="FFB7B7B7"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B7B7B7"/>
+        <color rgb="FFB7B7B7"/>
       </bottom>
       <diagonal/>
     </border>
@@ -742,7 +766,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -762,6 +786,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1063,18 +1094,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1106,7 +1134,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
@@ -1130,7 +1158,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>16</v>
       </c>
@@ -1158,7 +1186,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
@@ -1184,7 +1212,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>31</v>
       </c>
@@ -1212,7 +1240,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>39</v>
       </c>
@@ -1242,7 +1270,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>48</v>
       </c>
@@ -1268,7 +1296,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>55</v>
       </c>
@@ -1296,7 +1324,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>63</v>
       </c>
@@ -1312,24 +1340,36 @@
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
     </row>
+    <row r="10" spans="1:10" ht="28" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="9" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1358,225 +1398,252 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>65</v>
+        <v>185</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>66</v>
+        <v>186</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="D2" s="4"/>
+      <c r="D2" s="4" t="s">
+        <v>67</v>
+      </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+    </row>
+    <row r="4" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4" t="s">
+      <c r="D4" s="4"/>
+      <c r="E4" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="4" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="5" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B5" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4" t="s">
-        <v>84</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>90</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D8" s="4"/>
+        <v>96</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>97</v>
+      </c>
       <c r="E8" s="4" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="9" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I10" s="4" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="10" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="11" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4" t="s">
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-    </row>
-    <row r="11" ht="48" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+    </row>
+    <row r="12" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B12" s="6" t="s">
         <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -1585,18 +1652,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J12"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1628,7 +1692,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>117</v>
       </c>
@@ -1656,7 +1720,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>125</v>
       </c>
@@ -1686,7 +1750,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>68</v>
       </c>
@@ -1716,7 +1780,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>142</v>
       </c>
@@ -1740,7 +1804,7 @@
       </c>
       <c r="J5" s="4"/>
     </row>
-    <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>147</v>
       </c>
@@ -1766,7 +1830,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>154</v>
       </c>
@@ -1790,7 +1854,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>160</v>
       </c>
@@ -1814,7 +1878,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>166</v>
       </c>
@@ -1836,7 +1900,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>171</v>
       </c>
@@ -1860,7 +1924,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="11" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>177</v>
       </c>
@@ -1882,7 +1946,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="12" ht="48" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>182</v>
       </c>

--- a/content/backtrack2abq/data/dance-schedule.xlsx
+++ b/content/backtrack2abq/data/dance-schedule.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10726"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16E6C9D-744A-A144-BEEF-F54B2BECA524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{285CDF4D-628C-1C40-AAAD-D508DFF3B7AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="34900" windowHeight="19580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="34900" windowHeight="19580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thursday July 2" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="188">
   <si>
     <t>Time</t>
   </si>
@@ -682,6 +682,9 @@
   </si>
   <si>
     <t>* Brunch</t>
+  </si>
+  <si>
+    <t>5:00p-8:00p</t>
   </si>
 </sst>
 </file>
@@ -766,7 +769,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -786,13 +789,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1341,19 +1338,19 @@
       <c r="J9" s="4"/>
     </row>
     <row r="10" spans="1:10" ht="28" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1653,7 +1650,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1954,6 +1951,14 @@
         <v>116</v>
       </c>
     </row>
+    <row r="13" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>184</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/content/backtrack2abq/data/dance-schedule.xlsx
+++ b/content/backtrack2abq/data/dance-schedule.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10726"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{285CDF4D-628C-1C40-AAAD-D508DFF3B7AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="620" windowWidth="34900" windowHeight="19580" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="34900" windowHeight="19580" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Thursday July 2" sheetId="1" r:id="rId1"/>
-    <sheet name="Friday July 3" sheetId="2" r:id="rId2"/>
-    <sheet name="Saturday July 4" sheetId="3" r:id="rId3"/>
+    <sheet sheetId="1" name="Thursday July 2" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Friday July 3" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Saturday July 4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="186">
   <si>
     <t>Time</t>
   </si>
@@ -52,556 +51,562 @@
     <t>12:30p-1:30p</t>
   </si>
   <si>
-    <t>Plus : Dancing - Kris Jensen
+    <t xml:space="preserve">Plus : Dancing - Kris Jensen
 GCA: Tim Stephens</t>
   </si>
   <si>
-    <t>C3B : Dancing - Barry Clasper
+    <t xml:space="preserve">C3B : Dancing - Barry Clasper
 GCA: Osamu Miyabe</t>
   </si>
   <si>
-    <t>SSD : Dancing - Justin Russell
+    <t xml:space="preserve">SSD : Dancing - Justin Russell
 GCA: Patrick Aubert</t>
   </si>
   <si>
     <t>C1 &amp; C2 : Dancing - Vic Ceder</t>
   </si>
   <si>
-    <t>A1 : Dancing - Michael Kellogg
+    <t xml:space="preserve">A1 : Dancing - Michael Kellogg
 GCA: Andy Chong</t>
   </si>
   <si>
     <t>1:30p-2:30p</t>
   </si>
   <si>
-    <t>A2 : Dancing - Don Moger
+    <t xml:space="preserve">A2 : Dancing - Don Moger
 GCA: Jenn Engimann</t>
   </si>
   <si>
-    <t>C2 : Dancing - Rob French
+    <t xml:space="preserve">C2 : Dancing - Rob French
 GCA: Michael Maltenfort</t>
   </si>
   <si>
     <t>SSD : Skirt Work Hour - Wendy VanderMeulen</t>
   </si>
   <si>
-    <t>Plus : Dancing - Michael Kellogg
+    <t xml:space="preserve">Plus : Dancing - Michael Kellogg
 GCA: Michael Levy</t>
   </si>
   <si>
     <t>SSD : Dancing - Ted Lizotte</t>
   </si>
   <si>
-    <t>C3A : Dancing - Sandie Bryant
+    <t xml:space="preserve">C3A : Dancing - Sandie Bryant
 GCA: Jane Clewe</t>
   </si>
   <si>
-    <t>C1 : Dancing - Kris Jensen
+    <t xml:space="preserve">C1 : Dancing - Kris Jensen
 GCA: Fen Tamanaha</t>
   </si>
   <si>
     <t>2:30p-3:30p</t>
   </si>
   <si>
-    <t>A1 : Dancing - Ted Lizotte
+    <t xml:space="preserve">A1 : Dancing - Ted Lizotte
 GCA: Terri Sherrer</t>
   </si>
   <si>
-    <t>C2 : Dancing - Kris Jensen
+    <t xml:space="preserve">C2 : Dancing - Kris Jensen
 GCA: Andy Chong</t>
   </si>
   <si>
-    <t>Plus : Dancing - Wendy VanderMeulen
+    <t xml:space="preserve">Plus : Dancing - Wendy VanderMeulen
 GCA: Karla Westphal</t>
   </si>
   <si>
-    <t>SSD : Dancing - Michael Kellogg
+    <t xml:space="preserve">SSD : Dancing - Michael Kellogg
 GCA: John Ryan</t>
   </si>
   <si>
-    <t>C3B : Dancing - Rob French
+    <t xml:space="preserve">C3B : Dancing - Rob French
 GCA: John Hawley</t>
   </si>
   <si>
-    <t>C1 : Dancing - Don Moger
+    <t xml:space="preserve">C1 : Dancing - Don Moger
 GCA: Rick Hawes</t>
   </si>
   <si>
     <t>3:30p-4:30p</t>
   </si>
   <si>
-    <t>A2 : Dancing - Rob French
+    <t xml:space="preserve">A2 : Dancing - Rob French
 GCA: Michael Maltenfort</t>
   </si>
   <si>
-    <t>C2 : Dancing - Sandie Bryant
+    <t xml:space="preserve">C2 : Dancing - Sandie Bryant
 GCA: Dave Decot</t>
   </si>
   <si>
-    <t>Plus : Dancing - Justin Russell
+    <t xml:space="preserve">Plus : Dancing - Justin Russell
 GCA: Mary Thurston</t>
   </si>
   <si>
-    <t>SSD : Dancing - Wendy VanderMeulen
+    <t xml:space="preserve">SSD : Dancing - Wendy VanderMeulen
 GCA: Tim Stephens</t>
   </si>
   <si>
-    <t>C4 : Dancing - Vic Ceder
+    <t xml:space="preserve">C4 : Dancing - Vic Ceder
 GCA: John Ryan</t>
   </si>
   <si>
-    <t>C3A : Dancing - Vic Ceder
+    <t xml:space="preserve">C1 : Dancing - Barry Clasper
+GCA: Jane Clewe</t>
+  </si>
+  <si>
+    <t>7:00p-8:00p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2 : Dancing - Ted Lizotte
+GCA: Rick Hawes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2 : Dancing - Rob French
+GCA: Kent Forrester</t>
+  </si>
+  <si>
+    <t>SSD : Leather Tip - Michael Kellogg &amp; Terri Sherrer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Don Moger
+GCA: David Hartman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Justin Russell
+GCA: Mike Neiheisel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3A : Dancing - Vic Ceder
+GCA: John Hawley</t>
+  </si>
+  <si>
+    <t>Various : Zoom Reunion Hour - Ett McAtee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Sandie Bryant
+GCA: Osamu Miyabe</t>
+  </si>
+  <si>
+    <t>8:00p-9:00p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1 : Dancing - Kris Jensen
+GCA: Karla Westphal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2 : Dancing - Don Moger
+GCA: John Hawley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Justin Russell
+GCA: Janienne A-K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Vic Ceder
+GCA: Rick Hawes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3B : Dancing - Sandie Bryant
+GCA: Michael Maltenfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Ted Lizotte
+GCA: Brian Jarvis</t>
+  </si>
+  <si>
+    <t>9:00p-10:00p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2 : Dancing - Justin Russell
+GCA: David Hartman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2 : Dancing - Barry Clasper
+GCA: Jane Clewe</t>
+  </si>
+  <si>
+    <t>SSD : Glowstick Hour - Dave Hutchinson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Ted Lizotte
+GCA: Mary Thurston</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Kris Jensen
+GCA: Patti Cummings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C4 : Dancing - Rob French
+GCA: Bill van Melle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Michael Kellogg
+GCA: Michel Maltenfort</t>
+  </si>
+  <si>
+    <t>10:00p-11:00p</t>
+  </si>
+  <si>
+    <t>SSD : Zombie Callers - Various</t>
+  </si>
+  <si>
+    <t>4:30p-7:00p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* Dinner Break
+ROOMS: NONE</t>
+  </si>
+  <si>
+    <t>8:30-10:00a</t>
+  </si>
+  <si>
+    <t>* Brunch</t>
+  </si>
+  <si>
+    <t>"</t>
+  </si>
+  <si>
+    <t>10:15a-11:00a</t>
+  </si>
+  <si>
+    <t>SSD : All Callers Dance - All Callers</t>
+  </si>
+  <si>
+    <t>11:00a-12:00p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Sandie Bryant
+GCA: Michael Levy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Ted Lizotte
+GCA: Karla Westphal</t>
+  </si>
+  <si>
+    <t>C3A : Dancing - Don Moger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Dayle Hodge
+GCA: Tim Stephens</t>
+  </si>
+  <si>
+    <t>C2 : Dancing - Michael Kellogg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2 : Dancing - Justin Russell
+GCA: Osamu Miyabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2 : Dancing - Ted Lizotte
+GCA: Dave Decot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2 : Dancing - Vic Ceder
+GCA: Terri Sherrer</t>
+  </si>
+  <si>
+    <t>SSD : Women's Tip - Jenn Engimann &amp; Marge Coahran</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Kris Jensen
+GCA: David Hartman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Don Moger
+GCA: J.M. Robichaud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3A : Dancing - Sandie Bryant
+GCA: Osamu Miyabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Michael Kellogg
+GCA: Kent Forrester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1 : Dancing - Justin Russell
+GCA: Osamu Miyabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2 : Dancing - Barry Clasper
+GCA: John Hawley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Ted Lizotte
+GCA: Allan Hurst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Michael Kellogg
+GCA: Kurt Gollhardt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3B : Dancing - Vic Ceder
+GCA: Harlan Kerr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Rob French
+GCA: Bill van Melle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2 : Dancing - Sandie Bryant
+GCA: Harlan Kerr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2 : Dancing - Don Moger
+GCA: Andy Chong</t>
+  </si>
+  <si>
+    <t>SSD : Bear Tip - Kurt Gollhardt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Michael Kellogg
 GCA: Jenn Engimann</t>
   </si>
   <si>
-    <t>C1 : Dancing - Barry Clasper
+    <t xml:space="preserve">SSD : Dancing - Kris Jensen
+GCA: Allan Hurst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C4 : Dancing - Rob French
 GCA: Jane Clewe</t>
   </si>
   <si>
-    <t>7:00p-8:00p</t>
-  </si>
-  <si>
-    <t>A2 : Dancing - Ted Lizotte
+    <t xml:space="preserve">C1 : Dancing - Ted Lizotte
+GCA: Dave Decot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2 : Intro to C1 - Vic Ceder
+GCA: David Hartman</t>
+  </si>
+  <si>
+    <t>C2 : Dancing - Sandie Bryant</t>
+  </si>
+  <si>
+    <t>Intro : Intro to Square Dancing - Don Moger</t>
+  </si>
+  <si>
+    <t>Plus : Intro to A1 - Rick Hawes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Dave Hutchinson
+GCA: Greg Moore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3A : Dancing - Rob French
+GCA: Jane Clewe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Kris Jensen
+GCA: Andy Chong</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1 : Dancing - Barry Clasper
+GCA: Karla Westphal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2 : Dancing - Michael Kellogg
+GCA: Osamu Miyabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Justin Russell
+GCA: Tim Stephens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Intro to Plus - Ted Lizotte
+GCA: Patrick Aubert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3B : Dancing - Sandie Bryant
+GCA: Bill van Melle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Rob French
+GCA: Jenn Engimann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2 : Dancing - Michael Kellogg
+GCA: Kurt Gollhardt</t>
+  </si>
+  <si>
+    <t>C2 : Dancing - Kris Jensen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Sandie Bryant
+GCA: Mike Neiheisel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Justin Russell
+GCA: Greg Moore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C4 : Dancing - Barry Clasper
+GCA: Harlan Kerr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Vic Ceder
 GCA: Rick Hawes</t>
   </si>
   <si>
-    <t>C2 : Dancing - Rob French
+    <t>SSD : Moonshine Tip - Dayle Hodge &amp; Karla Westphal</t>
+  </si>
+  <si>
+    <t>12:00p-1:30p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* Lunch Break
+ROOMS: NONE</t>
+  </si>
+  <si>
+    <t>9:00a-10:00a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2 : Dancing - Michael Kellogg
+GCA: Karla Westphal</t>
+  </si>
+  <si>
+    <t>C2 : Dancing - Rob French</t>
+  </si>
+  <si>
+    <t>A1/A2 : Advanced Hothash - Justin Russell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Vic Ceder
+GCA: David Hartman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Kris Jensen
+GCA: Karin Rabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3A : Dancing - Barry Clasper
+GCA: Michael Maltenfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Ted Lizotte
 GCA: Kent Forrester</t>
   </si>
   <si>
-    <t>SSD : Leather Tip - Michael Kellogg &amp; Terri Sherrer</t>
-  </si>
-  <si>
-    <t>Plus : Dancing - Don Moger
+    <t>10:00a-11:00a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A2 : Dancing - Barry Clasper
+GCA: Dave Decot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2 : Dancing - Kris Jensen
+GCA: Osamu Miyabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Plus TNP - Ted Lizotte
+GCA: Michael Levy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Justin Russell
+GCA: Michael Maltenfort</t>
+  </si>
+  <si>
+    <t>* Intro to calling - Bill Eyler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Vic Ceder
+GCA: Kent Forrester</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3B : Dancing - Rob French
+GCA: Ryo Sasaki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Don Moger
+GCA: Harlan Kerr</t>
+  </si>
+  <si>
+    <t>A1 : Dancing - Ted Lizotte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2 : Dancing - Vic Ceder
+GCA: Fen Tamanaha</t>
+  </si>
+  <si>
+    <t>SSD : Kilt Tip - Brian Crawford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Don Moger
+GCA: Karin Rabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Allan Hurst
+GCA: Patrick Aubert</t>
+  </si>
+  <si>
+    <t>C4 : Dancing - Sandie Bryant</t>
+  </si>
+  <si>
+    <t>C2 : Dancing - Dave Hutchinson</t>
+  </si>
+  <si>
+    <t>A2 : Dancing - Kris Jensen</t>
+  </si>
+  <si>
+    <t>2:00p-3:00p</t>
+  </si>
+  <si>
+    <t>Plus : Dancing - Sandie Bryant</t>
+  </si>
+  <si>
+    <t>C3A : Dancing - Michael Kellogg</t>
+  </si>
+  <si>
+    <t>C1 : Dancing - Dayle Hodge</t>
+  </si>
+  <si>
+    <t>3:00p-4:00p</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Brian Crawford
+GCA: Rick Hawes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C3B : Dancing - Barry Clasper
+GCA: Harlan Kerr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Michael Kellogg
+GCA: Patti Cummings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 : Dancing - Rob French
+GCA: Osamu Miyabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2 : Dancing - Dayle Hodge
+GCA: Bill van Melle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Sandie Bryant
 GCA: David Hartman</t>
   </si>
   <si>
-    <t>SSD : Dancing - Justin Russell
-GCA: Mike Neiheisel</t>
-  </si>
-  <si>
-    <t>C3A : Dancing - Vic Ceder
-GCA: John Hawley</t>
-  </si>
-  <si>
-    <t>Various : Zoom Reunion Hour - Ett McAtee</t>
-  </si>
-  <si>
-    <t>C1 : Dancing - Sandie Bryant
-GCA: Osamu Miyabe</t>
-  </si>
-  <si>
-    <t>8:00p-9:00p</t>
-  </si>
-  <si>
-    <t>A1 : Dancing - Kris Jensen
-GCA: Karla Westphal</t>
-  </si>
-  <si>
-    <t>C2 : Dancing - Don Moger
-GCA: John Hawley</t>
-  </si>
-  <si>
-    <t>Plus : Dancing - Justin Russell
-GCA: Janienne A-K</t>
-  </si>
-  <si>
-    <t>SSD : Dancing - Vic Ceder
-GCA: Rick Hawes</t>
-  </si>
-  <si>
-    <t>C3B : Dancing - Sandie Bryant
+    <t>4:00p-5:00p</t>
+  </si>
+  <si>
+    <t>C4 : Dancing - Vic Ceder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSD : Dancing - Justin Russell
+GCA: Brian Jarvis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C1 &amp; C2 : Dancing - Kris Jensen
+GCA: Jenn Engimann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plus : Dancing - Dayle Hodge
 GCA: Michael Maltenfort</t>
   </si>
   <si>
-    <t>C1 : Dancing - Ted Lizotte
-GCA: Brian Jarvis</t>
-  </si>
-  <si>
-    <t>9:00p-10:00p</t>
-  </si>
-  <si>
-    <t>A2 : Dancing - Justin Russell
+    <t xml:space="preserve">A2 : Dancing - Sandie Bryant
 GCA: David Hartman</t>
   </si>
   <si>
-    <t>C2 : Dancing - Barry Clasper
-GCA: Jane Clewe</t>
-  </si>
-  <si>
-    <t>SSD : Glowstick Hour - Dave Hutchinson</t>
-  </si>
-  <si>
-    <t>Plus : Dancing - Ted Lizotte
-GCA: Mary Thurston</t>
-  </si>
-  <si>
-    <t>SSD : Dancing - Kris Jensen
-GCA: Patti Cummings</t>
-  </si>
-  <si>
-    <t>C4 : Dancing - Rob French
-GCA: Bill van Melle</t>
-  </si>
-  <si>
-    <t>C1 : Dancing - Michael Kellogg
-GCA: Michel Maltenfort</t>
-  </si>
-  <si>
-    <t>10:00p-11:00p</t>
-  </si>
-  <si>
-    <t>SSD : Zombie Callers - Various</t>
-  </si>
-  <si>
-    <t>10:15a-11:00a</t>
-  </si>
-  <si>
-    <t>SSD : All Callers Dance - All Callers</t>
-  </si>
-  <si>
-    <t>"</t>
-  </si>
-  <si>
-    <t>11:00a-12:00p</t>
-  </si>
-  <si>
-    <t>C1 : Dancing - Sandie Bryant
-GCA: Michael Levy</t>
-  </si>
-  <si>
-    <t>Plus : Dancing - Ted Lizotte
-GCA: Karla Westphal</t>
-  </si>
-  <si>
-    <t>C3A : Dancing - Don Moger</t>
-  </si>
-  <si>
-    <t>SSD : Dancing - Dayle Hodge
-GCA: Tim Stephens</t>
-  </si>
-  <si>
-    <t>C2 : Dancing - Michael Kellogg</t>
-  </si>
-  <si>
-    <t>A2 : Dancing - Justin Russell
-GCA: Osamu Miyabe</t>
-  </si>
-  <si>
-    <t>A2 : Dancing - Ted Lizotte
-GCA: Dave Decot</t>
-  </si>
-  <si>
-    <t>C2 : Dancing - Vic Ceder
-GCA: Terri Sherrer</t>
-  </si>
-  <si>
-    <t>SSD : Women's Tip - Jenn Engimann &amp; Marge Coahran</t>
-  </si>
-  <si>
-    <t>Plus : Dancing - Kris Jensen
-GCA: David Hartman</t>
-  </si>
-  <si>
-    <t>SSD : Dancing - Don Moger
-GCA: J.M. Robichaud</t>
-  </si>
-  <si>
-    <t>C3A : Dancing - Sandie Bryant
-GCA: Osamu Miyabe</t>
-  </si>
-  <si>
-    <t>C1 : Dancing - Michael Kellogg
-GCA: Kent Forrester</t>
-  </si>
-  <si>
-    <t>A1 : Dancing - Justin Russell
-GCA: Osamu Miyabe</t>
-  </si>
-  <si>
-    <t>C2 : Dancing - Barry Clasper
-GCA: John Hawley</t>
-  </si>
-  <si>
-    <t>Plus : Dancing - Ted Lizotte
-GCA: Allan Hurst</t>
-  </si>
-  <si>
-    <t>SSD : Dancing - Michael Kellogg
-GCA: Kurt Gollhardt</t>
-  </si>
-  <si>
-    <t>C3B : Dancing - Vic Ceder
-GCA: Harlan Kerr</t>
-  </si>
-  <si>
-    <t>C1 : Dancing - Rob French
-GCA: Bill van Melle</t>
-  </si>
-  <si>
-    <t>A2 : Dancing - Sandie Bryant
-GCA: Harlan Kerr</t>
-  </si>
-  <si>
-    <t>C2 : Dancing - Don Moger
-GCA: Andy Chong</t>
-  </si>
-  <si>
-    <t>SSD : Bear Tip - Kurt Gollhardt</t>
-  </si>
-  <si>
-    <t>Plus : Dancing - Michael Kellogg
-GCA: Jenn Engimann</t>
-  </si>
-  <si>
-    <t>SSD : Dancing - Kris Jensen
-GCA: Allan Hurst</t>
-  </si>
-  <si>
-    <t>C4 : Dancing - Rob French
-GCA: Jane Clewe</t>
-  </si>
-  <si>
-    <t>C1 : Dancing - Ted Lizotte
-GCA: Dave Decot</t>
-  </si>
-  <si>
-    <t>A2 : Intro to C1 - Vic Ceder
-GCA: David Hartman</t>
-  </si>
-  <si>
-    <t>C2 : Dancing - Sandie Bryant</t>
-  </si>
-  <si>
-    <t>Intro : Intro to Square Dancing - Don Moger</t>
-  </si>
-  <si>
-    <t>Plus : Intro to A1 - Rick Hawes</t>
-  </si>
-  <si>
-    <t>SSD : Dancing - Dave Hutchinson
-GCA: Greg Moore</t>
-  </si>
-  <si>
-    <t>C3A : Dancing - Rob French
-GCA: Jane Clewe</t>
-  </si>
-  <si>
-    <t>C1 : Dancing - Kris Jensen
-GCA: Andy Chong</t>
-  </si>
-  <si>
-    <t>A1 : Dancing - Barry Clasper
-GCA: Karla Westphal</t>
-  </si>
-  <si>
-    <t>C2 : Dancing - Michael Kellogg
-GCA: Osamu Miyabe</t>
-  </si>
-  <si>
-    <t>Plus : Dancing - Justin Russell
-GCA: Tim Stephens</t>
-  </si>
-  <si>
-    <t>SSD : Intro to Plus - Ted Lizotte
-GCA: Patrick Aubert</t>
-  </si>
-  <si>
-    <t>C3B : Dancing - Sandie Bryant
-GCA: Bill van Melle</t>
-  </si>
-  <si>
-    <t>C1 : Dancing - Rob French
-GCA: Jenn Engimann</t>
-  </si>
-  <si>
-    <t>A2 : Dancing - Michael Kellogg
-GCA: Kurt Gollhardt</t>
-  </si>
-  <si>
-    <t>C2 : Dancing - Kris Jensen</t>
-  </si>
-  <si>
-    <t>Plus : Dancing - Sandie Bryant
-GCA: Mike Neiheisel</t>
-  </si>
-  <si>
-    <t>SSD : Dancing - Justin Russell
-GCA: Greg Moore</t>
-  </si>
-  <si>
-    <t>C4 : Dancing - Barry Clasper
-GCA: Harlan Kerr</t>
-  </si>
-  <si>
-    <t>C1 : Dancing - Vic Ceder
-GCA: Rick Hawes</t>
-  </si>
-  <si>
-    <t>SSD : Moonshine Tip - Dayle Hodge &amp; Karla Westphal</t>
-  </si>
-  <si>
-    <t>12:00p-1:30p</t>
-  </si>
-  <si>
-    <t>* Lunch Break
-ROOMS: NONE</t>
-  </si>
-  <si>
-    <t>9:00a-10:00a</t>
-  </si>
-  <si>
-    <t>A2 : Dancing - Michael Kellogg
-GCA: Karla Westphal</t>
-  </si>
-  <si>
-    <t>C2 : Dancing - Rob French</t>
-  </si>
-  <si>
-    <t>A1/A2 : Advanced Hothash - Justin Russell</t>
-  </si>
-  <si>
-    <t>Plus : Dancing - Vic Ceder
-GCA: David Hartman</t>
-  </si>
-  <si>
-    <t>SSD : Dancing - Kris Jensen
-GCA: Karin Rabe</t>
-  </si>
-  <si>
-    <t>C3A : Dancing - Barry Clasper
-GCA: Michael Maltenfort</t>
-  </si>
-  <si>
-    <t>C1 : Dancing - Ted Lizotte
-GCA: Kent Forrester</t>
-  </si>
-  <si>
-    <t>10:00a-11:00a</t>
-  </si>
-  <si>
-    <t>A2 : Dancing - Barry Clasper
-GCA: Dave Decot</t>
-  </si>
-  <si>
-    <t>C2 : Dancing - Kris Jensen
-GCA: Osamu Miyabe</t>
-  </si>
-  <si>
-    <t>Plus : Plus TNP - Ted Lizotte
-GCA: Michael Levy</t>
-  </si>
-  <si>
-    <t>Plus : Dancing - Justin Russell
-GCA: Michael Maltenfort</t>
-  </si>
-  <si>
-    <t>* Intro to calling - Bill Eyler</t>
-  </si>
-  <si>
-    <t>SSD : Dancing - Vic Ceder
-GCA: Kent Forrester</t>
-  </si>
-  <si>
-    <t>C3B : Dancing - Rob French
-GCA: Ryo Sasaki</t>
-  </si>
-  <si>
-    <t>C1 : Dancing - Don Moger
-GCA: Harlan Kerr</t>
-  </si>
-  <si>
-    <t>A1 : Dancing - Ted Lizotte</t>
-  </si>
-  <si>
-    <t>C2 : Dancing - Vic Ceder
-GCA: Fen Tamanaha</t>
-  </si>
-  <si>
-    <t>SSD : Kilt Tip - Brian Crawford</t>
-  </si>
-  <si>
-    <t>Plus : Dancing - Don Moger
-GCA: Karin Rabe</t>
-  </si>
-  <si>
-    <t>SSD : Dancing - Allan Hurst
-GCA: Patrick Aubert</t>
-  </si>
-  <si>
-    <t>C4 : Dancing - Sandie Bryant</t>
-  </si>
-  <si>
-    <t>C2 : Dancing - Dave Hutchinson</t>
-  </si>
-  <si>
-    <t>A2 : Dancing - Kris Jensen</t>
-  </si>
-  <si>
-    <t>2:00p-3:00p</t>
-  </si>
-  <si>
-    <t>Plus : Dancing - Sandie Bryant</t>
-  </si>
-  <si>
-    <t>C3A : Dancing - Michael Kellogg</t>
-  </si>
-  <si>
-    <t>C1 : Dancing - Dayle Hodge</t>
-  </si>
-  <si>
-    <t>C2 : Dancing - Dayle Hodge</t>
-  </si>
-  <si>
-    <t>3:00p-4:00p</t>
-  </si>
-  <si>
-    <t>Plus : Dancing - Brian Crawford
-GCA: Rick Hawes</t>
-  </si>
-  <si>
-    <t>C3B : Dancing - Barry Clasper
-GCA: Harlan Kerr</t>
-  </si>
-  <si>
-    <t>SSD : Dancing - Michael Kellogg
-GCA: Patti Cummings</t>
-  </si>
-  <si>
-    <t>C1 : Dancing - Rob French
-GCA: Osamu Miyabe</t>
-  </si>
-  <si>
-    <t>C2 : Dancing - Dayle Hodge
-GCA: Bill van Melle</t>
-  </si>
-  <si>
-    <t>Plus : Dancing - Sandie Bryant
-GCA: David Hartman</t>
-  </si>
-  <si>
-    <t>4:00p-5:00p</t>
-  </si>
-  <si>
-    <t>C4 : Dancing - Vic Ceder</t>
-  </si>
-  <si>
-    <t>SSD : Dancing - Justin Russell
-GCA: Brian Jarvis</t>
-  </si>
-  <si>
-    <t>C1 &amp; C2 : Dancing - Kris Jensen
-GCA: Jenn Engimann</t>
-  </si>
-  <si>
-    <t>Plus : Dancing - Dayle Hodge
-GCA: Michael Maltenfort</t>
-  </si>
-  <si>
-    <t>A2 : Dancing - Sandie Bryant
-GCA: David Hartman</t>
-  </si>
-  <si>
     <t>8:00p-8:30p</t>
   </si>
   <si>
@@ -669,19 +674,6 @@
   </si>
   <si>
     <t>12:00p-2:00p</t>
-  </si>
-  <si>
-    <t>4:30p-7:00p</t>
-  </si>
-  <si>
-    <t>* Dinner Break
-ROOMS: NONE</t>
-  </si>
-  <si>
-    <t>8:30-10:00a</t>
-  </si>
-  <si>
-    <t>* Brunch</t>
   </si>
   <si>
     <t>5:00p-8:00p</t>
@@ -690,42 +682,42 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
+      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -737,9 +729,6 @@
         <fgColor rgb="FF1F4E78"/>
         <bgColor rgb="FF1F4E78"/>
       </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="2">
@@ -777,10 +766,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1091,15 +1080,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="8.83203125"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1131,7 +1120,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
@@ -1155,7 +1144,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>16</v>
       </c>
@@ -1183,7 +1172,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
@@ -1209,7 +1198,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>31</v>
       </c>
@@ -1231,118 +1220,118 @@
         <v>36</v>
       </c>
       <c r="I5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="4" t="s">
+    </row>
+    <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="J6" s="4" t="s">
+    </row>
+    <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="C7" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="F8" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>60</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:10" ht="28" x14ac:dyDescent="0.2">
+    <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>183</v>
+        <v>64</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>184</v>
+        <v>65</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1358,15 +1347,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="8.83203125"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="9" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1395,18 +1384,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>185</v>
+        <v>66</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>186</v>
+        <v>67</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
@@ -1414,15 +1403,15 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -1431,195 +1420,195 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="F6" s="4"/>
       <c r="G6" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F9" s="4"/>
       <c r="G9" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F10" s="4"/>
       <c r="G10" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
@@ -1627,20 +1616,20 @@
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
     </row>
-    <row r="12" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" ht="48" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>183</v>
+        <v>64</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>184</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1649,15 +1638,15 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.2" defaultColWidth="8.83203125"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1689,274 +1678,274 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="J5" s="4"/>
     </row>
-    <row r="6" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="12" ht="48" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" ht="48" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>184</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/content/backtrack2abq/data/dance-schedule.xlsx
+++ b/content/backtrack2abq/data/dance-schedule.xlsx
@@ -10,13 +10,15 @@
     <sheet sheetId="1" name="Thursday July 2" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Friday July 3" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Saturday July 4" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="- Hours by Level" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="- Hours by Caller" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="238">
   <si>
     <t>Time</t>
   </si>
@@ -677,13 +679,172 @@
   </si>
   <si>
     <t>5:00p-8:00p</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>Plus</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>C3A</t>
+  </si>
+  <si>
+    <t>C3B</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>Intro</t>
+  </si>
+  <si>
+    <t>Various</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Thu, Jul 2</t>
+  </si>
+  <si>
+    <t>Fri, Jul 3</t>
+  </si>
+  <si>
+    <t>Sat, Jul 4</t>
+  </si>
+  <si>
+    <t>Generated by scripts/generate-dance-schedule-hour-tabs.ts — re-run after editing any day's schedule.</t>
+  </si>
+  <si>
+    <t>All Callers</t>
+  </si>
+  <si>
+    <t>Allan Hurst</t>
+  </si>
+  <si>
+    <t>Barry Clasper</t>
+  </si>
+  <si>
+    <t>Bill van Melle</t>
+  </si>
+  <si>
+    <t>Brian Crawford</t>
+  </si>
+  <si>
+    <t>Brian Jarvis</t>
+  </si>
+  <si>
+    <t>Dave Hutchinson</t>
+  </si>
+  <si>
+    <t>David Hartman</t>
+  </si>
+  <si>
+    <t>Dayle Hodge</t>
+  </si>
+  <si>
+    <t>Don Moger</t>
+  </si>
+  <si>
+    <t>Ett McAtee</t>
+  </si>
+  <si>
+    <t>Greg Moore</t>
+  </si>
+  <si>
+    <t>Jane Clewe</t>
+  </si>
+  <si>
+    <t>Janienne Alexander</t>
+  </si>
+  <si>
+    <t>Jenn Engimann</t>
+  </si>
+  <si>
+    <t>John Hawley</t>
+  </si>
+  <si>
+    <t>Justin Russell</t>
+  </si>
+  <si>
+    <t>Karin Rabe</t>
+  </si>
+  <si>
+    <t>Karla Westphal</t>
+  </si>
+  <si>
+    <t>Kris Jensen</t>
+  </si>
+  <si>
+    <t>Kurt Gollhardt</t>
+  </si>
+  <si>
+    <t>Marge Coahran</t>
+  </si>
+  <si>
+    <t>Michael Kellogg</t>
+  </si>
+  <si>
+    <t>Michael Levy</t>
+  </si>
+  <si>
+    <t>Michael Maltenfort</t>
+  </si>
+  <si>
+    <t>Patrick Aubert</t>
+  </si>
+  <si>
+    <t>Rick Hawes</t>
+  </si>
+  <si>
+    <t>Rob French</t>
+  </si>
+  <si>
+    <t>Ryo Sasaki</t>
+  </si>
+  <si>
+    <t>Sandie Bryant</t>
+  </si>
+  <si>
+    <t>Ted Lizotte</t>
+  </si>
+  <si>
+    <t>Terri Sherrer</t>
+  </si>
+  <si>
+    <t>Tim Stephens</t>
+  </si>
+  <si>
+    <t>Vic Ceder</t>
+  </si>
+  <si>
+    <t>Wendy VanderMeulen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -715,6 +876,9 @@
       <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
     </font>
   </fonts>
   <fills count="3">
@@ -758,7 +922,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -779,6 +943,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1951,4 +2118,923 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M7"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="2" max="2" width="9" style="8" customWidth="1"/>
+    <col min="3" max="3" width="9" style="8" customWidth="1"/>
+    <col min="4" max="4" width="9" style="8" customWidth="1"/>
+    <col min="5" max="5" width="9" style="8" customWidth="1"/>
+    <col min="6" max="6" width="9" style="8" customWidth="1"/>
+    <col min="7" max="7" width="9" style="8" customWidth="1"/>
+    <col min="8" max="8" width="9" style="8" customWidth="1"/>
+    <col min="9" max="9" width="9" style="8" customWidth="1"/>
+    <col min="10" max="10" width="9" style="8" customWidth="1"/>
+    <col min="11" max="11" width="9" style="8" customWidth="1"/>
+    <col min="12" max="12" width="9" style="8" customWidth="1"/>
+    <col min="13" max="13" width="9" style="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B2" s="8">
+        <v>11</v>
+      </c>
+      <c r="C2" s="8">
+        <v>7</v>
+      </c>
+      <c r="D2" s="8">
+        <v>3</v>
+      </c>
+      <c r="E2" s="8">
+        <v>4</v>
+      </c>
+      <c r="F2" s="8">
+        <v>7.5</v>
+      </c>
+      <c r="G2" s="8">
+        <v>6.5</v>
+      </c>
+      <c r="H2" s="8">
+        <v>2</v>
+      </c>
+      <c r="I2" s="8">
+        <v>3</v>
+      </c>
+      <c r="J2" s="8">
+        <v>2</v>
+      </c>
+      <c r="K2" s="8">
+        <v>0</v>
+      </c>
+      <c r="L2" s="8">
+        <v>1</v>
+      </c>
+      <c r="M2" s="8">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B3" s="8">
+        <v>10.75</v>
+      </c>
+      <c r="C3" s="8">
+        <v>7</v>
+      </c>
+      <c r="D3" s="8">
+        <v>2</v>
+      </c>
+      <c r="E3" s="8">
+        <v>5</v>
+      </c>
+      <c r="F3" s="8">
+        <v>7</v>
+      </c>
+      <c r="G3" s="8">
+        <v>7</v>
+      </c>
+      <c r="H3" s="8">
+        <v>3</v>
+      </c>
+      <c r="I3" s="8">
+        <v>2</v>
+      </c>
+      <c r="J3" s="8">
+        <v>2</v>
+      </c>
+      <c r="K3" s="8">
+        <v>1</v>
+      </c>
+      <c r="L3" s="8">
+        <v>0</v>
+      </c>
+      <c r="M3" s="8">
+        <v>46.75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B4" s="8">
+        <v>9</v>
+      </c>
+      <c r="C4" s="8">
+        <v>10.5</v>
+      </c>
+      <c r="D4" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="E4" s="8">
+        <v>6.5</v>
+      </c>
+      <c r="F4" s="8">
+        <v>5.75</v>
+      </c>
+      <c r="G4" s="8">
+        <v>5.75</v>
+      </c>
+      <c r="H4" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="I4" s="8">
+        <v>2</v>
+      </c>
+      <c r="J4" s="8">
+        <v>2</v>
+      </c>
+      <c r="K4" s="8">
+        <v>0</v>
+      </c>
+      <c r="L4" s="8">
+        <v>0</v>
+      </c>
+      <c r="M4" s="8">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B5" s="10">
+        <v>30.75</v>
+      </c>
+      <c r="C5" s="10">
+        <v>24.5</v>
+      </c>
+      <c r="D5" s="10">
+        <v>7.5</v>
+      </c>
+      <c r="E5" s="10">
+        <v>15.5</v>
+      </c>
+      <c r="F5" s="10">
+        <v>20.25</v>
+      </c>
+      <c r="G5" s="10">
+        <v>19.25</v>
+      </c>
+      <c r="H5" s="10">
+        <v>7.5</v>
+      </c>
+      <c r="I5" s="10">
+        <v>7</v>
+      </c>
+      <c r="J5" s="10">
+        <v>6</v>
+      </c>
+      <c r="K5" s="10">
+        <v>1</v>
+      </c>
+      <c r="L5" s="10">
+        <v>1</v>
+      </c>
+      <c r="M5" s="10">
+        <v>140.25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AL7"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="2" max="2" width="9" style="8" customWidth="1"/>
+    <col min="3" max="3" width="9" style="8" customWidth="1"/>
+    <col min="4" max="4" width="9" style="8" customWidth="1"/>
+    <col min="5" max="5" width="9" style="8" customWidth="1"/>
+    <col min="6" max="6" width="9" style="8" customWidth="1"/>
+    <col min="7" max="7" width="9" style="8" customWidth="1"/>
+    <col min="8" max="8" width="9" style="8" customWidth="1"/>
+    <col min="9" max="9" width="9" style="8" customWidth="1"/>
+    <col min="10" max="10" width="9" style="8" customWidth="1"/>
+    <col min="11" max="11" width="9" style="8" customWidth="1"/>
+    <col min="12" max="12" width="9" style="8" customWidth="1"/>
+    <col min="13" max="13" width="9" style="8" customWidth="1"/>
+    <col min="14" max="14" width="9" style="8" customWidth="1"/>
+    <col min="15" max="15" width="9" style="8" customWidth="1"/>
+    <col min="16" max="16" width="9" style="8" customWidth="1"/>
+    <col min="17" max="17" width="9" style="8" customWidth="1"/>
+    <col min="18" max="18" width="9" style="8" customWidth="1"/>
+    <col min="19" max="19" width="9" style="8" customWidth="1"/>
+    <col min="20" max="20" width="9" style="8" customWidth="1"/>
+    <col min="21" max="21" width="9" style="8" customWidth="1"/>
+    <col min="22" max="22" width="9" style="8" customWidth="1"/>
+    <col min="23" max="23" width="9" style="8" customWidth="1"/>
+    <col min="24" max="24" width="9" style="8" customWidth="1"/>
+    <col min="25" max="25" width="9" style="8" customWidth="1"/>
+    <col min="26" max="26" width="9" style="8" customWidth="1"/>
+    <col min="27" max="27" width="9" style="8" customWidth="1"/>
+    <col min="28" max="28" width="9" style="8" customWidth="1"/>
+    <col min="29" max="29" width="9" style="8" customWidth="1"/>
+    <col min="30" max="30" width="9" style="8" customWidth="1"/>
+    <col min="31" max="31" width="9" style="8" customWidth="1"/>
+    <col min="32" max="32" width="9" style="8" customWidth="1"/>
+    <col min="33" max="33" width="9" style="8" customWidth="1"/>
+    <col min="34" max="34" width="9" style="8" customWidth="1"/>
+    <col min="35" max="35" width="9" style="8" customWidth="1"/>
+    <col min="36" max="36" width="9" style="8" customWidth="1"/>
+    <col min="37" max="37" width="9" style="8" customWidth="1"/>
+    <col min="38" max="38" width="9" style="8" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:38" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="R1" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="S1" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="T1" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="U1" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="V1" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="W1" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="X1" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="Y1" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="Z1" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="AA1" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="AB1" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="AC1" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="AD1" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="AE1" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="AF1" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="AG1" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="AH1" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="AI1" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="AJ1" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="AK1" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="AL1" s="10" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B2" s="8">
+        <v>0</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0</v>
+      </c>
+      <c r="D2" s="8">
+        <v>3</v>
+      </c>
+      <c r="E2" s="8">
+        <v>0</v>
+      </c>
+      <c r="F2" s="8">
+        <v>0</v>
+      </c>
+      <c r="G2" s="8">
+        <v>0</v>
+      </c>
+      <c r="H2" s="8">
+        <v>1</v>
+      </c>
+      <c r="I2" s="8">
+        <v>0</v>
+      </c>
+      <c r="J2" s="8">
+        <v>0</v>
+      </c>
+      <c r="K2" s="8">
+        <v>5</v>
+      </c>
+      <c r="L2" s="8">
+        <v>1</v>
+      </c>
+      <c r="M2" s="8">
+        <v>0</v>
+      </c>
+      <c r="N2" s="8">
+        <v>0</v>
+      </c>
+      <c r="O2" s="8">
+        <v>0</v>
+      </c>
+      <c r="P2" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="8">
+        <v>0</v>
+      </c>
+      <c r="R2" s="8">
+        <v>5</v>
+      </c>
+      <c r="S2" s="8">
+        <v>0</v>
+      </c>
+      <c r="T2" s="8">
+        <v>0</v>
+      </c>
+      <c r="U2" s="8">
+        <v>5</v>
+      </c>
+      <c r="V2" s="8">
+        <v>0</v>
+      </c>
+      <c r="W2" s="8">
+        <v>0</v>
+      </c>
+      <c r="X2" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="Y2" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="8">
+        <v>5</v>
+      </c>
+      <c r="AD2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="8">
+        <v>4</v>
+      </c>
+      <c r="AF2" s="8">
+        <v>5</v>
+      </c>
+      <c r="AG2" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="AH2" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="8">
+        <v>1</v>
+      </c>
+      <c r="AJ2" s="8">
+        <v>4</v>
+      </c>
+      <c r="AK2" s="8">
+        <v>3</v>
+      </c>
+      <c r="AL2" s="8">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>200</v>
+      </c>
+      <c r="B3" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0</v>
+      </c>
+      <c r="D3" s="8">
+        <v>3</v>
+      </c>
+      <c r="E3" s="8">
+        <v>0</v>
+      </c>
+      <c r="F3" s="8">
+        <v>0</v>
+      </c>
+      <c r="G3" s="8">
+        <v>0</v>
+      </c>
+      <c r="H3" s="8">
+        <v>1</v>
+      </c>
+      <c r="I3" s="8">
+        <v>0</v>
+      </c>
+      <c r="J3" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="K3" s="8">
+        <v>4</v>
+      </c>
+      <c r="L3" s="8">
+        <v>0</v>
+      </c>
+      <c r="M3" s="8">
+        <v>0</v>
+      </c>
+      <c r="N3" s="8">
+        <v>0</v>
+      </c>
+      <c r="O3" s="8">
+        <v>0</v>
+      </c>
+      <c r="P3" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>0</v>
+      </c>
+      <c r="R3" s="8">
+        <v>4</v>
+      </c>
+      <c r="S3" s="8">
+        <v>0</v>
+      </c>
+      <c r="T3" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U3" s="8">
+        <v>4</v>
+      </c>
+      <c r="V3" s="8">
+        <v>1</v>
+      </c>
+      <c r="W3" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="X3" s="8">
+        <v>6</v>
+      </c>
+      <c r="Y3" s="8">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AA3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AB3" s="8">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="8">
+        <v>4</v>
+      </c>
+      <c r="AD3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="8">
+        <v>6</v>
+      </c>
+      <c r="AF3" s="8">
+        <v>5</v>
+      </c>
+      <c r="AG3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="8">
+        <v>4</v>
+      </c>
+      <c r="AK3" s="8">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="8">
+        <v>46.75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B4" s="8">
+        <v>0</v>
+      </c>
+      <c r="C4" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="D4" s="8">
+        <v>3</v>
+      </c>
+      <c r="E4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="F4" s="8">
+        <v>2</v>
+      </c>
+      <c r="G4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H4" s="8">
+        <v>1</v>
+      </c>
+      <c r="I4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="J4" s="8">
+        <v>3</v>
+      </c>
+      <c r="K4" s="8">
+        <v>2</v>
+      </c>
+      <c r="L4" s="8">
+        <v>0</v>
+      </c>
+      <c r="M4" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="N4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="O4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="P4" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="R4" s="8">
+        <v>3</v>
+      </c>
+      <c r="S4" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="T4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="U4" s="8">
+        <v>5</v>
+      </c>
+      <c r="V4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W4" s="8">
+        <v>0</v>
+      </c>
+      <c r="X4" s="8">
+        <v>3</v>
+      </c>
+      <c r="Y4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Z4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="AA4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="AB4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="AC4" s="8">
+        <v>3</v>
+      </c>
+      <c r="AD4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="AE4" s="8">
+        <v>4</v>
+      </c>
+      <c r="AF4" s="8">
+        <v>4</v>
+      </c>
+      <c r="AG4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="AI4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="AK4" s="8">
+        <v>0</v>
+      </c>
+      <c r="AL4" s="8">
+        <v>46.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="B5" s="10">
+        <v>0.75</v>
+      </c>
+      <c r="C5" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="D5" s="10">
+        <v>9</v>
+      </c>
+      <c r="E5" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="10">
+        <v>2</v>
+      </c>
+      <c r="G5" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="H5" s="10">
+        <v>3</v>
+      </c>
+      <c r="I5" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="J5" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="K5" s="10">
+        <v>11</v>
+      </c>
+      <c r="L5" s="10">
+        <v>1</v>
+      </c>
+      <c r="M5" s="10">
+        <v>0.25</v>
+      </c>
+      <c r="N5" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="O5" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="P5" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="R5" s="10">
+        <v>12</v>
+      </c>
+      <c r="S5" s="10">
+        <v>0.25</v>
+      </c>
+      <c r="T5" s="10">
+        <v>1</v>
+      </c>
+      <c r="U5" s="10">
+        <v>14</v>
+      </c>
+      <c r="V5" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="W5" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="X5" s="10">
+        <v>13.5</v>
+      </c>
+      <c r="Y5" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="Z5" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AA5" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AB5" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="AC5" s="10">
+        <v>12</v>
+      </c>
+      <c r="AD5" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AE5" s="10">
+        <v>14</v>
+      </c>
+      <c r="AF5" s="10">
+        <v>14</v>
+      </c>
+      <c r="AG5" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AH5" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AI5" s="10">
+        <v>1</v>
+      </c>
+      <c r="AJ5" s="10">
+        <v>12.5</v>
+      </c>
+      <c r="AK5" s="10">
+        <v>3</v>
+      </c>
+      <c r="AL5" s="10">
+        <v>140.25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="8"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="8"/>
+      <c r="R7" s="8"/>
+      <c r="S7" s="8"/>
+      <c r="T7" s="8"/>
+      <c r="U7" s="8"/>
+      <c r="V7" s="8"/>
+      <c r="W7" s="8"/>
+      <c r="X7" s="8"/>
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="8"/>
+      <c r="AA7" s="8"/>
+      <c r="AB7" s="8"/>
+      <c r="AC7" s="8"/>
+      <c r="AD7" s="8"/>
+      <c r="AE7" s="8"/>
+      <c r="AF7" s="8"/>
+      <c r="AG7" s="8"/>
+      <c r="AH7" s="8"/>
+      <c r="AI7" s="8"/>
+      <c r="AJ7" s="8"/>
+      <c r="AK7" s="8"/>
+      <c r="AL7" s="8"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>
--- a/content/backtrack2abq/data/dance-schedule.xlsx
+++ b/content/backtrack2abq/data/dance-schedule.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="240">
   <si>
     <t>Time</t>
   </si>
@@ -732,109 +732,115 @@
     <t>Generated by scripts/generate-dance-schedule-hour-tabs.ts — re-run after editing any day's schedule.</t>
   </si>
   <si>
+    <t>Calculated at:</t>
+  </si>
+  <si>
+    <t>Status:</t>
+  </si>
+  <si>
+    <t>Kris Jensen</t>
+  </si>
+  <si>
+    <t>Sandie Bryant</t>
+  </si>
+  <si>
+    <t>Ted Lizotte</t>
+  </si>
+  <si>
+    <t>Michael Kellogg</t>
+  </si>
+  <si>
+    <t>Vic Ceder</t>
+  </si>
+  <si>
+    <t>Justin Russell</t>
+  </si>
+  <si>
+    <t>Rob French</t>
+  </si>
+  <si>
+    <t>Don Moger</t>
+  </si>
+  <si>
+    <t>Barry Clasper</t>
+  </si>
+  <si>
+    <t>Dayle Hodge</t>
+  </si>
+  <si>
+    <t>Dave Hutchinson</t>
+  </si>
+  <si>
+    <t>Wendy VanderMeulen</t>
+  </si>
+  <si>
+    <t>Brian Crawford</t>
+  </si>
+  <si>
+    <t>Allan Hurst</t>
+  </si>
+  <si>
+    <t>Kurt Gollhardt</t>
+  </si>
+  <si>
+    <t>Rick Hawes</t>
+  </si>
+  <si>
+    <t>Ett McAtee</t>
+  </si>
+  <si>
+    <t>Karla Westphal</t>
+  </si>
+  <si>
     <t>All Callers</t>
   </si>
   <si>
-    <t>Allan Hurst</t>
-  </si>
-  <si>
-    <t>Barry Clasper</t>
+    <t>Jenn Engimann</t>
+  </si>
+  <si>
+    <t>Marge Coahran</t>
+  </si>
+  <si>
+    <t>Terri Sherrer</t>
   </si>
   <si>
     <t>Bill van Melle</t>
   </si>
   <si>
-    <t>Brian Crawford</t>
-  </si>
-  <si>
     <t>Brian Jarvis</t>
   </si>
   <si>
-    <t>Dave Hutchinson</t>
-  </si>
-  <si>
     <t>David Hartman</t>
   </si>
   <si>
-    <t>Dayle Hodge</t>
-  </si>
-  <si>
-    <t>Don Moger</t>
-  </si>
-  <si>
-    <t>Ett McAtee</t>
+    <t>Jane Clewe</t>
+  </si>
+  <si>
+    <t>Janienne Alexander</t>
+  </si>
+  <si>
+    <t>John Hawley</t>
+  </si>
+  <si>
+    <t>Michael Levy</t>
+  </si>
+  <si>
+    <t>Michael Maltenfort</t>
+  </si>
+  <si>
+    <t>Patrick Aubert</t>
+  </si>
+  <si>
+    <t>Ryo Sasaki</t>
+  </si>
+  <si>
+    <t>Tim Stephens</t>
   </si>
   <si>
     <t>Greg Moore</t>
   </si>
   <si>
-    <t>Jane Clewe</t>
-  </si>
-  <si>
-    <t>Janienne Alexander</t>
-  </si>
-  <si>
-    <t>Jenn Engimann</t>
-  </si>
-  <si>
-    <t>John Hawley</t>
-  </si>
-  <si>
-    <t>Justin Russell</t>
-  </si>
-  <si>
     <t>Karin Rabe</t>
-  </si>
-  <si>
-    <t>Karla Westphal</t>
-  </si>
-  <si>
-    <t>Kris Jensen</t>
-  </si>
-  <si>
-    <t>Kurt Gollhardt</t>
-  </si>
-  <si>
-    <t>Marge Coahran</t>
-  </si>
-  <si>
-    <t>Michael Kellogg</t>
-  </si>
-  <si>
-    <t>Michael Levy</t>
-  </si>
-  <si>
-    <t>Michael Maltenfort</t>
-  </si>
-  <si>
-    <t>Patrick Aubert</t>
-  </si>
-  <si>
-    <t>Rick Hawes</t>
-  </si>
-  <si>
-    <t>Rob French</t>
-  </si>
-  <si>
-    <t>Ryo Sasaki</t>
-  </si>
-  <si>
-    <t>Sandie Bryant</t>
-  </si>
-  <si>
-    <t>Ted Lizotte</t>
-  </si>
-  <si>
-    <t>Terri Sherrer</t>
-  </si>
-  <si>
-    <t>Tim Stephens</t>
-  </si>
-  <si>
-    <t>Vic Ceder</t>
-  </si>
-  <si>
-    <t>Wendy VanderMeulen</t>
   </si>
 </sst>
 </file>
@@ -895,7 +901,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -918,11 +924,18 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -946,6 +959,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2122,7 +2137,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="9" style="8" customWidth="1"/>
@@ -2361,6 +2376,45 @@
       <c r="L7" s="8"/>
       <c r="M7" s="8"/>
     </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>203</v>
+      </c>
+      <c r="B8" s="8">
+        <v>46240.62467592592</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>204</v>
+      </c>
+      <c r="B9" s="8" t="str">
+        <f>IF(NOW()&gt;B8+TIME(0,2,0),"⚠ Recalculated since Calculated-at — totals may be stale, re-run the generator script","✓ Up to date as of the Calculated-at time above")</f>
+        <v>✓ Up to date as of the Calculated-at time above</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2369,7 +2423,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL7"/>
+  <dimension ref="A1:AL9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="2" max="2" width="9" style="8" customWidth="1"/>
@@ -2416,112 +2470,112 @@
         <v>186</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L1" s="10" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M1" s="10" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N1" s="10" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O1" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P1" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q1" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="R1" s="10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="S1" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="T1" s="10" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="U1" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="V1" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="W1" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="X1" s="10" t="s">
         <v>225</v>
       </c>
+      <c r="X1" s="11" t="s">
+        <v>226</v>
+      </c>
       <c r="Y1" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Z1" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AA1" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AB1" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AC1" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AD1" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AE1" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AF1" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG1" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AH1" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AI1" s="10" t="s">
-        <v>197</v>
+        <v>237</v>
       </c>
       <c r="AJ1" s="10" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AK1" s="10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AL1" s="10" t="s">
         <v>198</v>
@@ -2532,40 +2586,40 @@
         <v>199</v>
       </c>
       <c r="B2" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C2" s="8">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D2" s="8">
+        <v>5</v>
+      </c>
+      <c r="E2" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="F2" s="8">
+        <v>4</v>
+      </c>
+      <c r="G2" s="8">
+        <v>5</v>
+      </c>
+      <c r="H2" s="8">
+        <v>5</v>
+      </c>
+      <c r="I2" s="8">
+        <v>5</v>
+      </c>
+      <c r="J2" s="8">
         <v>3</v>
       </c>
-      <c r="E2" s="8">
-        <v>0</v>
-      </c>
-      <c r="F2" s="8">
-        <v>0</v>
-      </c>
-      <c r="G2" s="8">
-        <v>0</v>
-      </c>
-      <c r="H2" s="8">
-        <v>1</v>
-      </c>
-      <c r="I2" s="8">
-        <v>0</v>
-      </c>
-      <c r="J2" s="8">
-        <v>0</v>
-      </c>
       <c r="K2" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L2" s="8">
         <v>1</v>
       </c>
       <c r="M2" s="8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N2" s="8">
         <v>0</v>
@@ -2580,16 +2634,16 @@
         <v>0</v>
       </c>
       <c r="R2" s="8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S2" s="8">
         <v>0</v>
       </c>
       <c r="T2" s="8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V2" s="8">
         <v>0</v>
@@ -2597,8 +2651,8 @@
       <c r="W2" s="8">
         <v>0</v>
       </c>
-      <c r="X2" s="8">
-        <v>4.5</v>
+      <c r="X2" s="12">
+        <v>0.5</v>
       </c>
       <c r="Y2" s="8">
         <v>0</v>
@@ -2613,31 +2667,31 @@
         <v>0</v>
       </c>
       <c r="AC2" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AD2" s="8">
         <v>0</v>
       </c>
       <c r="AE2" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AF2" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AG2" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AH2" s="8">
         <v>0</v>
       </c>
       <c r="AI2" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ2" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AK2" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL2" s="8">
         <v>47</v>
@@ -2648,73 +2702,73 @@
         <v>200</v>
       </c>
       <c r="B3" s="8">
+        <v>4</v>
+      </c>
+      <c r="C3" s="8">
+        <v>6</v>
+      </c>
+      <c r="D3" s="8">
+        <v>5</v>
+      </c>
+      <c r="E3" s="8">
+        <v>6</v>
+      </c>
+      <c r="F3" s="8">
+        <v>4</v>
+      </c>
+      <c r="G3" s="8">
+        <v>4</v>
+      </c>
+      <c r="H3" s="8">
+        <v>4</v>
+      </c>
+      <c r="I3" s="8">
+        <v>4</v>
+      </c>
+      <c r="J3" s="8">
+        <v>3</v>
+      </c>
+      <c r="K3" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="L3" s="8">
+        <v>1</v>
+      </c>
+      <c r="M3" s="8">
+        <v>0</v>
+      </c>
+      <c r="N3" s="8">
+        <v>0</v>
+      </c>
+      <c r="O3" s="8">
+        <v>0</v>
+      </c>
+      <c r="P3" s="8">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="8">
+        <v>1</v>
+      </c>
+      <c r="R3" s="8">
+        <v>0</v>
+      </c>
+      <c r="S3" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="T3" s="8">
+        <v>0</v>
+      </c>
+      <c r="U3" s="8">
         <v>0.75</v>
       </c>
-      <c r="C3" s="8">
-        <v>0</v>
-      </c>
-      <c r="D3" s="8">
-        <v>3</v>
-      </c>
-      <c r="E3" s="8">
-        <v>0</v>
-      </c>
-      <c r="F3" s="8">
-        <v>0</v>
-      </c>
-      <c r="G3" s="8">
-        <v>0</v>
-      </c>
-      <c r="H3" s="8">
-        <v>1</v>
-      </c>
-      <c r="I3" s="8">
-        <v>0</v>
-      </c>
-      <c r="J3" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="K3" s="8">
-        <v>4</v>
-      </c>
-      <c r="L3" s="8">
-        <v>0</v>
-      </c>
-      <c r="M3" s="8">
-        <v>0</v>
-      </c>
-      <c r="N3" s="8">
-        <v>0</v>
-      </c>
-      <c r="O3" s="8">
-        <v>0</v>
-      </c>
-      <c r="P3" s="8">
+      <c r="V3" s="8">
         <v>0.5</v>
-      </c>
-      <c r="Q3" s="8">
-        <v>0</v>
-      </c>
-      <c r="R3" s="8">
-        <v>4</v>
-      </c>
-      <c r="S3" s="8">
-        <v>0</v>
-      </c>
-      <c r="T3" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="U3" s="8">
-        <v>4</v>
-      </c>
-      <c r="V3" s="8">
-        <v>1</v>
       </c>
       <c r="W3" s="8">
         <v>0.5</v>
       </c>
-      <c r="X3" s="8">
-        <v>6</v>
+      <c r="X3" s="12">
+        <v>0</v>
       </c>
       <c r="Y3" s="8">
         <v>0</v>
@@ -2726,19 +2780,19 @@
         <v>0</v>
       </c>
       <c r="AB3" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD3" s="8">
         <v>0</v>
       </c>
       <c r="AE3" s="8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AF3" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AG3" s="8">
         <v>0</v>
@@ -2750,7 +2804,7 @@
         <v>0</v>
       </c>
       <c r="AJ3" s="8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AK3" s="8">
         <v>0</v>
@@ -2764,73 +2818,73 @@
         <v>201</v>
       </c>
       <c r="B4" s="8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C4" s="8">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="8">
+        <v>4</v>
+      </c>
+      <c r="E4" s="8">
         <v>3</v>
       </c>
-      <c r="E4" s="8">
-        <v>0.5</v>
-      </c>
       <c r="F4" s="8">
+        <v>4.5</v>
+      </c>
+      <c r="G4" s="8">
+        <v>3</v>
+      </c>
+      <c r="H4" s="8">
+        <v>3</v>
+      </c>
+      <c r="I4" s="8">
         <v>2</v>
-      </c>
-      <c r="G4" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H4" s="8">
-        <v>1</v>
-      </c>
-      <c r="I4" s="8">
-        <v>0.5</v>
       </c>
       <c r="J4" s="8">
         <v>3</v>
       </c>
       <c r="K4" s="8">
+        <v>3</v>
+      </c>
+      <c r="L4" s="8">
+        <v>1</v>
+      </c>
+      <c r="M4" s="8">
+        <v>0</v>
+      </c>
+      <c r="N4" s="8">
         <v>2</v>
       </c>
-      <c r="L4" s="8">
-        <v>0</v>
-      </c>
-      <c r="M4" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="N4" s="8">
+      <c r="O4" s="8">
+        <v>1.5</v>
+      </c>
+      <c r="P4" s="8">
         <v>0.5</v>
-      </c>
-      <c r="O4" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="P4" s="8">
-        <v>0</v>
       </c>
       <c r="Q4" s="8">
         <v>0.5</v>
       </c>
       <c r="R4" s="8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S4" s="8">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="T4" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="U4" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V4" s="8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W4" s="8">
         <v>0</v>
       </c>
-      <c r="X4" s="8">
-        <v>3</v>
+      <c r="X4" s="12">
+        <v>0</v>
       </c>
       <c r="Y4" s="8">
         <v>0.5</v>
@@ -2845,31 +2899,31 @@
         <v>0.5</v>
       </c>
       <c r="AC4" s="8">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="AD4" s="8">
         <v>0.5</v>
       </c>
       <c r="AE4" s="8">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="AF4" s="8">
-        <v>4</v>
+        <v>0.5</v>
       </c>
       <c r="AG4" s="8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AH4" s="8">
         <v>0.5</v>
       </c>
       <c r="AI4" s="8">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AJ4" s="8">
-        <v>4.5</v>
+        <v>0.25</v>
       </c>
       <c r="AK4" s="8">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AL4" s="8">
         <v>46.5</v>
@@ -2880,73 +2934,73 @@
         <v>198</v>
       </c>
       <c r="B5" s="10">
-        <v>0.75</v>
+        <v>14</v>
       </c>
       <c r="C5" s="10">
+        <v>14</v>
+      </c>
+      <c r="D5" s="10">
+        <v>14</v>
+      </c>
+      <c r="E5" s="10">
+        <v>13.5</v>
+      </c>
+      <c r="F5" s="10">
+        <v>12.5</v>
+      </c>
+      <c r="G5" s="10">
+        <v>12</v>
+      </c>
+      <c r="H5" s="10">
+        <v>12</v>
+      </c>
+      <c r="I5" s="10">
+        <v>11</v>
+      </c>
+      <c r="J5" s="10">
+        <v>9</v>
+      </c>
+      <c r="K5" s="10">
+        <v>4.5</v>
+      </c>
+      <c r="L5" s="10">
+        <v>3</v>
+      </c>
+      <c r="M5" s="10">
+        <v>3</v>
+      </c>
+      <c r="N5" s="10">
+        <v>2</v>
+      </c>
+      <c r="O5" s="10">
         <v>1.5</v>
       </c>
-      <c r="D5" s="10">
-        <v>9</v>
-      </c>
-      <c r="E5" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="F5" s="10">
-        <v>2</v>
-      </c>
-      <c r="G5" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="H5" s="10">
-        <v>3</v>
-      </c>
-      <c r="I5" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="J5" s="10">
-        <v>4.5</v>
-      </c>
-      <c r="K5" s="10">
-        <v>11</v>
-      </c>
-      <c r="L5" s="10">
+      <c r="P5" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>1.5</v>
+      </c>
+      <c r="R5" s="10">
         <v>1</v>
       </c>
-      <c r="M5" s="10">
-        <v>0.25</v>
-      </c>
-      <c r="N5" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="O5" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="P5" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="Q5" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="R5" s="10">
-        <v>12</v>
-      </c>
       <c r="S5" s="10">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="T5" s="10">
         <v>1</v>
       </c>
       <c r="U5" s="10">
-        <v>14</v>
+        <v>0.75</v>
       </c>
       <c r="V5" s="10">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="W5" s="10">
         <v>0.5</v>
       </c>
-      <c r="X5" s="10">
-        <v>13.5</v>
+      <c r="X5" s="11">
+        <v>0.5</v>
       </c>
       <c r="Y5" s="10">
         <v>0.5</v>
@@ -2958,19 +3012,19 @@
         <v>0.5</v>
       </c>
       <c r="AB5" s="10">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="AC5" s="10">
-        <v>12</v>
+        <v>0.5</v>
       </c>
       <c r="AD5" s="10">
         <v>0.5</v>
       </c>
       <c r="AE5" s="10">
-        <v>14</v>
+        <v>0.5</v>
       </c>
       <c r="AF5" s="10">
-        <v>14</v>
+        <v>0.5</v>
       </c>
       <c r="AG5" s="10">
         <v>0.5</v>
@@ -2979,13 +3033,13 @@
         <v>0.5</v>
       </c>
       <c r="AI5" s="10">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AJ5" s="10">
-        <v>12.5</v>
+        <v>0.25</v>
       </c>
       <c r="AK5" s="10">
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="AL5" s="10">
         <v>140.25</v>
@@ -3033,6 +3087,95 @@
       <c r="AK7" s="8"/>
       <c r="AL7" s="8"/>
     </row>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>203</v>
+      </c>
+      <c r="B8" s="8">
+        <v>46240.62467592592</v>
+      </c>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+      <c r="W8" s="8"/>
+      <c r="X8" s="8"/>
+      <c r="Y8" s="8"/>
+      <c r="Z8" s="8"/>
+      <c r="AA8" s="8"/>
+      <c r="AB8" s="8"/>
+      <c r="AC8" s="8"/>
+      <c r="AD8" s="8"/>
+      <c r="AE8" s="8"/>
+      <c r="AF8" s="8"/>
+      <c r="AG8" s="8"/>
+      <c r="AH8" s="8"/>
+      <c r="AI8" s="8"/>
+      <c r="AJ8" s="8"/>
+      <c r="AK8" s="8"/>
+      <c r="AL8" s="8"/>
+    </row>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>204</v>
+      </c>
+      <c r="B9" s="8" t="str">
+        <f>IF(NOW()&gt;B8+TIME(0,2,0),"⚠ Recalculated since Calculated-at — totals may be stale, re-run the generator script","✓ Up to date as of the Calculated-at time above")</f>
+        <v>✓ Up to date as of the Calculated-at time above</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="8"/>
+      <c r="W9" s="8"/>
+      <c r="X9" s="8"/>
+      <c r="Y9" s="8"/>
+      <c r="Z9" s="8"/>
+      <c r="AA9" s="8"/>
+      <c r="AB9" s="8"/>
+      <c r="AC9" s="8"/>
+      <c r="AD9" s="8"/>
+      <c r="AE9" s="8"/>
+      <c r="AF9" s="8"/>
+      <c r="AG9" s="8"/>
+      <c r="AH9" s="8"/>
+      <c r="AI9" s="8"/>
+      <c r="AJ9" s="8"/>
+      <c r="AK9" s="8"/>
+      <c r="AL9" s="8"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/content/backtrack2abq/data/dance-schedule.xlsx
+++ b/content/backtrack2abq/data/dance-schedule.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="241">
   <si>
     <t>Time</t>
   </si>
@@ -729,13 +729,16 @@
     <t>Sat, Jul 4</t>
   </si>
   <si>
+    <t>Calculated</t>
+  </si>
+  <si>
+    <t>Saved</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
     <t>Generated by scripts/generate-dance-schedule-hour-tabs.ts — re-run after editing any day's schedule.</t>
-  </si>
-  <si>
-    <t>Calculated at:</t>
-  </si>
-  <si>
-    <t>Status:</t>
   </si>
   <si>
     <t>Kris Jensen</t>
@@ -848,7 +851,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -956,11 +959,11 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="19" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2137,61 +2140,51 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="2" max="2" width="9" style="8" customWidth="1"/>
-    <col min="3" max="3" width="9" style="8" customWidth="1"/>
-    <col min="4" max="4" width="9" style="8" customWidth="1"/>
-    <col min="5" max="5" width="9" style="8" customWidth="1"/>
-    <col min="6" max="6" width="9" style="8" customWidth="1"/>
-    <col min="7" max="7" width="9" style="8" customWidth="1"/>
-    <col min="8" max="8" width="9" style="8" customWidth="1"/>
-    <col min="9" max="9" width="9" style="8" customWidth="1"/>
-    <col min="10" max="10" width="9" style="8" customWidth="1"/>
-    <col min="11" max="11" width="9" style="8" customWidth="1"/>
-    <col min="12" max="12" width="9" style="8" customWidth="1"/>
-    <col min="13" max="13" width="9" style="8" customWidth="1"/>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="13" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="8" t="s">
         <v>190</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="8" t="s">
         <v>192</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="8" t="s">
         <v>193</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="8" t="s">
         <v>198</v>
       </c>
     </row>
@@ -2199,40 +2192,40 @@
       <c r="A2" t="s">
         <v>199</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2">
         <v>11</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2">
         <v>7</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2">
         <v>3</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2">
         <v>4</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2">
         <v>7.5</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2">
         <v>6.5</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2">
         <v>2</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2">
         <v>3</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2">
         <v>2</v>
       </c>
-      <c r="K2" s="8">
-        <v>0</v>
-      </c>
-      <c r="L2" s="8">
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
         <v>1</v>
       </c>
-      <c r="M2" s="8">
+      <c r="M2">
         <v>47</v>
       </c>
     </row>
@@ -2240,40 +2233,40 @@
       <c r="A3" t="s">
         <v>200</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3">
         <v>10.75</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3">
         <v>7</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3">
         <v>2</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3">
         <v>5</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3">
         <v>7</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3">
         <v>7</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3">
         <v>3</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3">
         <v>2</v>
       </c>
-      <c r="J3" s="8">
+      <c r="J3">
         <v>2</v>
       </c>
-      <c r="K3" s="8">
+      <c r="K3">
         <v>1</v>
       </c>
-      <c r="L3" s="8">
-        <v>0</v>
-      </c>
-      <c r="M3" s="8">
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
         <v>46.75</v>
       </c>
     </row>
@@ -2281,139 +2274,121 @@
       <c r="A4" t="s">
         <v>201</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4">
         <v>9</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4">
         <v>10.5</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4">
         <v>2.5</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4">
         <v>6.5</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4">
         <v>5.75</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4">
         <v>5.75</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4">
         <v>2.5</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4">
         <v>2</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4">
         <v>2</v>
       </c>
-      <c r="K4" s="8">
-        <v>0</v>
-      </c>
-      <c r="L4" s="8">
-        <v>0</v>
-      </c>
-      <c r="M4" s="8">
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
         <v>46.5</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="8">
         <v>30.75</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="8">
         <v>24.5</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="8">
         <v>7.5</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="8">
         <v>15.5</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="8">
         <v>20.25</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="8">
         <v>19.25</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="8">
         <v>7.5</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="8">
         <v>7</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="8">
         <v>6</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="8">
         <v>1</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="8">
         <v>1</v>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="8">
         <v>140.25</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>202</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B7" s="9">
+        <v>46240.67644675926</v>
+      </c>
+      <c r="C7" s="10">
+        <v>46240.67644675926</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>203</v>
       </c>
-      <c r="B8" s="8">
-        <v>46240.62467592592</v>
-      </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B8" s="9">
+        <f>NOW()</f>
+        <v>46240.67644675926</v>
+      </c>
+      <c r="C8" s="10">
+        <f>NOW()</f>
+        <v>46240.67644675926</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>204</v>
       </c>
-      <c r="B9" s="8" t="str">
-        <f>IF(NOW()&gt;B8+TIME(0,2,0),"⚠ Recalculated since Calculated-at — totals may be stale, re-run the generator script","✓ Up to date as of the Calculated-at time above")</f>
-        <v>✓ Up to date as of the Calculated-at time above</v>
-      </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
+      <c r="B9" t="str">
+        <f>IF(C8&gt;C7+TIME(0,0,15),"⚠ Recalculated since Saved — totals may be stale, re-run the generator script","✓ Up to date as of Saved")</f>
+        <v>✓ Up to date as of Saved</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>205</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2423,161 +2398,158 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL9"/>
+  <dimension ref="A1:AL10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="2" max="2" width="9" style="8" customWidth="1"/>
-    <col min="3" max="3" width="9" style="8" customWidth="1"/>
-    <col min="4" max="4" width="9" style="8" customWidth="1"/>
-    <col min="5" max="5" width="9" style="8" customWidth="1"/>
-    <col min="6" max="6" width="9" style="8" customWidth="1"/>
-    <col min="7" max="7" width="9" style="8" customWidth="1"/>
-    <col min="8" max="8" width="9" style="8" customWidth="1"/>
-    <col min="9" max="9" width="9" style="8" customWidth="1"/>
-    <col min="10" max="10" width="9" style="8" customWidth="1"/>
-    <col min="11" max="11" width="9" style="8" customWidth="1"/>
-    <col min="12" max="12" width="9" style="8" customWidth="1"/>
-    <col min="13" max="13" width="9" style="8" customWidth="1"/>
-    <col min="14" max="14" width="9" style="8" customWidth="1"/>
-    <col min="15" max="15" width="9" style="8" customWidth="1"/>
-    <col min="16" max="16" width="9" style="8" customWidth="1"/>
-    <col min="17" max="17" width="9" style="8" customWidth="1"/>
-    <col min="18" max="18" width="9" style="8" customWidth="1"/>
-    <col min="19" max="19" width="9" style="8" customWidth="1"/>
-    <col min="20" max="20" width="9" style="8" customWidth="1"/>
-    <col min="21" max="21" width="9" style="8" customWidth="1"/>
-    <col min="22" max="22" width="9" style="8" customWidth="1"/>
-    <col min="23" max="23" width="9" style="8" customWidth="1"/>
-    <col min="24" max="24" width="9" style="8" customWidth="1"/>
-    <col min="25" max="25" width="9" style="8" customWidth="1"/>
-    <col min="26" max="26" width="9" style="8" customWidth="1"/>
-    <col min="27" max="27" width="9" style="8" customWidth="1"/>
-    <col min="28" max="28" width="9" style="8" customWidth="1"/>
-    <col min="29" max="29" width="9" style="8" customWidth="1"/>
-    <col min="30" max="30" width="9" style="8" customWidth="1"/>
-    <col min="31" max="31" width="9" style="8" customWidth="1"/>
-    <col min="32" max="32" width="9" style="8" customWidth="1"/>
-    <col min="33" max="33" width="9" style="8" customWidth="1"/>
-    <col min="34" max="34" width="9" style="8" customWidth="1"/>
-    <col min="35" max="35" width="9" style="8" customWidth="1"/>
-    <col min="36" max="36" width="9" style="8" customWidth="1"/>
-    <col min="37" max="37" width="9" style="8" customWidth="1"/>
-    <col min="38" max="38" width="9" style="8" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="21" customWidth="1"/>
+    <col min="14" max="14" width="17" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="16" max="16" width="17" customWidth="1"/>
+    <col min="17" max="18" width="13" customWidth="1"/>
+    <col min="19" max="19" width="17" customWidth="1"/>
+    <col min="20" max="20" width="10" customWidth="1"/>
+    <col min="21" max="21" width="14" customWidth="1"/>
+    <col min="22" max="24" width="16" customWidth="1"/>
+    <col min="25" max="25" width="17" customWidth="1"/>
+    <col min="26" max="26" width="15" customWidth="1"/>
+    <col min="27" max="27" width="16" customWidth="1"/>
+    <col min="28" max="28" width="13" customWidth="1"/>
+    <col min="29" max="29" width="21" customWidth="1"/>
+    <col min="30" max="30" width="14" customWidth="1"/>
+    <col min="31" max="31" width="15" customWidth="1"/>
+    <col min="32" max="32" width="21" customWidth="1"/>
+    <col min="33" max="33" width="17" customWidth="1"/>
+    <col min="34" max="34" width="13" customWidth="1"/>
+    <col min="35" max="35" width="15" customWidth="1"/>
+    <col min="36" max="37" width="13" customWidth="1"/>
+    <col min="38" max="38" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="B1" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="C1" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="D1" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="E1" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="F1" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="G1" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="H1" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="I1" s="8" t="s">
         <v>213</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="J1" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="K1" s="8" t="s">
         <v>215</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="L1" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="M1" s="8" t="s">
         <v>217</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="N1" s="8" t="s">
         <v>218</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="O1" s="8" t="s">
         <v>219</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="P1" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="Q1" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="R1" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="S1" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="T1" s="8" t="s">
         <v>197</v>
       </c>
-      <c r="U1" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="V1" s="10" t="s">
+      <c r="U1" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="W1" s="10" t="s">
+      <c r="V1" s="8" t="s">
         <v>225</v>
       </c>
+      <c r="W1" s="8" t="s">
+        <v>226</v>
+      </c>
       <c r="X1" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="Y1" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="Z1" s="10" t="s">
+      <c r="Y1" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="AA1" s="10" t="s">
+      <c r="Z1" s="8" t="s">
         <v>229</v>
       </c>
-      <c r="AB1" s="10" t="s">
+      <c r="AA1" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="AC1" s="10" t="s">
+      <c r="AB1" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="AD1" s="10" t="s">
+      <c r="AC1" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="AE1" s="10" t="s">
+      <c r="AD1" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="AF1" s="10" t="s">
+      <c r="AE1" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="AG1" s="10" t="s">
+      <c r="AF1" s="8" t="s">
         <v>235</v>
       </c>
-      <c r="AH1" s="10" t="s">
+      <c r="AG1" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="AI1" s="10" t="s">
+      <c r="AH1" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="AJ1" s="10" t="s">
+      <c r="AI1" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="AK1" s="10" t="s">
+      <c r="AJ1" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="AL1" s="10" t="s">
+      <c r="AK1" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="AL1" s="8" t="s">
         <v>198</v>
       </c>
     </row>
@@ -2585,115 +2557,115 @@
       <c r="A2" t="s">
         <v>199</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2">
         <v>5</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2">
         <v>4</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D2">
         <v>5</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E2">
         <v>4.5</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2">
         <v>4</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2">
         <v>5</v>
       </c>
-      <c r="H2" s="8">
+      <c r="H2">
         <v>5</v>
       </c>
-      <c r="I2" s="8">
+      <c r="I2">
         <v>5</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2">
         <v>3</v>
       </c>
-      <c r="K2" s="8">
-        <v>0</v>
-      </c>
-      <c r="L2" s="8">
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
         <v>1</v>
       </c>
-      <c r="M2" s="8">
+      <c r="M2">
         <v>3</v>
       </c>
-      <c r="N2" s="8">
-        <v>0</v>
-      </c>
-      <c r="O2" s="8">
-        <v>0</v>
-      </c>
-      <c r="P2" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="8">
-        <v>0</v>
-      </c>
-      <c r="R2" s="8">
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
         <v>1</v>
       </c>
-      <c r="S2" s="8">
-        <v>0</v>
-      </c>
-      <c r="T2" s="8">
+      <c r="S2">
+        <v>0</v>
+      </c>
+      <c r="T2">
         <v>1</v>
       </c>
-      <c r="U2" s="8">
-        <v>0</v>
-      </c>
-      <c r="V2" s="8">
-        <v>0</v>
-      </c>
-      <c r="W2" s="8">
+      <c r="U2">
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
         <v>0</v>
       </c>
       <c r="X2" s="12">
         <v>0.5</v>
       </c>
-      <c r="Y2" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z2" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB2" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD2" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE2" s="8">
-        <v>0</v>
-      </c>
-      <c r="AF2" s="8">
-        <v>0</v>
-      </c>
-      <c r="AG2" s="8">
-        <v>0</v>
-      </c>
-      <c r="AH2" s="8">
-        <v>0</v>
-      </c>
-      <c r="AI2" s="8">
-        <v>0</v>
-      </c>
-      <c r="AJ2" s="8">
-        <v>0</v>
-      </c>
-      <c r="AK2" s="8">
-        <v>0</v>
-      </c>
-      <c r="AL2" s="8">
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>0</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
         <v>47</v>
       </c>
     </row>
@@ -2701,115 +2673,115 @@
       <c r="A3" t="s">
         <v>200</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3">
         <v>4</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3">
         <v>6</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3">
         <v>5</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3">
         <v>6</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3">
         <v>4</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3">
         <v>4</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3">
         <v>4</v>
       </c>
-      <c r="I3" s="8">
+      <c r="I3">
         <v>4</v>
       </c>
-      <c r="J3" s="8">
+      <c r="J3">
         <v>3</v>
       </c>
-      <c r="K3" s="8">
+      <c r="K3">
         <v>1.5</v>
       </c>
-      <c r="L3" s="8">
+      <c r="L3">
         <v>1</v>
       </c>
-      <c r="M3" s="8">
-        <v>0</v>
-      </c>
-      <c r="N3" s="8">
-        <v>0</v>
-      </c>
-      <c r="O3" s="8">
-        <v>0</v>
-      </c>
-      <c r="P3" s="8">
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
         <v>1</v>
       </c>
-      <c r="Q3" s="8">
+      <c r="Q3">
         <v>1</v>
       </c>
-      <c r="R3" s="8">
-        <v>0</v>
-      </c>
-      <c r="S3" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="T3" s="8">
-        <v>0</v>
-      </c>
-      <c r="U3" s="8">
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0.5</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
         <v>0.75</v>
       </c>
-      <c r="V3" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="W3" s="8">
+      <c r="V3">
+        <v>0.5</v>
+      </c>
+      <c r="W3">
         <v>0.5</v>
       </c>
       <c r="X3" s="12">
         <v>0</v>
       </c>
-      <c r="Y3" s="8">
-        <v>0</v>
-      </c>
-      <c r="Z3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AA3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AB3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AC3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AD3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AF3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AJ3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AK3" s="8">
-        <v>0</v>
-      </c>
-      <c r="AL3" s="8">
+      <c r="Y3">
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>0</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AI3">
+        <v>0</v>
+      </c>
+      <c r="AJ3">
+        <v>0</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3">
         <v>46.75</v>
       </c>
     </row>
@@ -2817,364 +2789,271 @@
       <c r="A4" t="s">
         <v>201</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4">
         <v>5</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4">
         <v>4</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4">
         <v>4</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4">
         <v>3</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4">
         <v>4.5</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4">
         <v>3</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4">
         <v>3</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4">
         <v>2</v>
       </c>
-      <c r="J4" s="8">
+      <c r="J4">
         <v>3</v>
       </c>
-      <c r="K4" s="8">
+      <c r="K4">
         <v>3</v>
       </c>
-      <c r="L4" s="8">
+      <c r="L4">
         <v>1</v>
       </c>
-      <c r="M4" s="8">
-        <v>0</v>
-      </c>
-      <c r="N4" s="8">
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
         <v>2</v>
       </c>
-      <c r="O4" s="8">
+      <c r="O4">
         <v>1.5</v>
       </c>
-      <c r="P4" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="Q4" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="R4" s="8">
-        <v>0</v>
-      </c>
-      <c r="S4" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="T4" s="8">
-        <v>0</v>
-      </c>
-      <c r="U4" s="8">
-        <v>0</v>
-      </c>
-      <c r="V4" s="8">
-        <v>0</v>
-      </c>
-      <c r="W4" s="8">
+      <c r="P4">
+        <v>0.5</v>
+      </c>
+      <c r="Q4">
+        <v>0.5</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0.5</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
         <v>0</v>
       </c>
       <c r="X4" s="12">
         <v>0</v>
       </c>
-      <c r="Y4" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="Z4" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="AA4" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="AB4" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="AC4" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="AD4" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="AE4" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="AF4" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="AG4" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="AH4" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="AI4" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="AJ4" s="8">
+      <c r="Y4">
+        <v>0.5</v>
+      </c>
+      <c r="Z4">
+        <v>0.5</v>
+      </c>
+      <c r="AA4">
+        <v>0.5</v>
+      </c>
+      <c r="AB4">
+        <v>0.5</v>
+      </c>
+      <c r="AC4">
+        <v>0.5</v>
+      </c>
+      <c r="AD4">
+        <v>0.5</v>
+      </c>
+      <c r="AE4">
+        <v>0.5</v>
+      </c>
+      <c r="AF4">
+        <v>0.5</v>
+      </c>
+      <c r="AG4">
+        <v>0.5</v>
+      </c>
+      <c r="AH4">
+        <v>0.5</v>
+      </c>
+      <c r="AI4">
+        <v>0.5</v>
+      </c>
+      <c r="AJ4">
         <v>0.25</v>
       </c>
-      <c r="AK4" s="8">
+      <c r="AK4">
         <v>0.25</v>
       </c>
-      <c r="AL4" s="8">
+      <c r="AL4">
         <v>46.5</v>
       </c>
     </row>
-    <row r="5" spans="1:38" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="8">
         <v>14</v>
       </c>
-      <c r="C5" s="10">
+      <c r="C5" s="8">
         <v>14</v>
       </c>
-      <c r="D5" s="10">
+      <c r="D5" s="8">
         <v>14</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="8">
         <v>13.5</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="8">
         <v>12.5</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="8">
         <v>12</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="8">
         <v>12</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="8">
         <v>11</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="8">
         <v>9</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="8">
         <v>4.5</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="8">
         <v>3</v>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="8">
         <v>3</v>
       </c>
-      <c r="N5" s="10">
+      <c r="N5" s="8">
         <v>2</v>
       </c>
-      <c r="O5" s="10">
+      <c r="O5" s="8">
         <v>1.5</v>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="8">
         <v>1.5</v>
       </c>
-      <c r="Q5" s="10">
+      <c r="Q5" s="8">
         <v>1.5</v>
       </c>
-      <c r="R5" s="10">
+      <c r="R5" s="8">
         <v>1</v>
       </c>
-      <c r="S5" s="10">
+      <c r="S5" s="8">
         <v>1</v>
       </c>
-      <c r="T5" s="10">
+      <c r="T5" s="8">
         <v>1</v>
       </c>
-      <c r="U5" s="10">
+      <c r="U5" s="8">
         <v>0.75</v>
       </c>
-      <c r="V5" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="W5" s="10">
+      <c r="V5" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="W5" s="8">
         <v>0.5</v>
       </c>
       <c r="X5" s="11">
         <v>0.5</v>
       </c>
-      <c r="Y5" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="Z5" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="AA5" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="AB5" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="AC5" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="AD5" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="AE5" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="AF5" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="AG5" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="AH5" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="AI5" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="AJ5" s="10">
+      <c r="Y5" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="Z5" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="AA5" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="AB5" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="AC5" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="AD5" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="AE5" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="AF5" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="AG5" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="AH5" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="AI5" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="AJ5" s="8">
         <v>0.25</v>
       </c>
-      <c r="AK5" s="10">
+      <c r="AK5" s="8">
         <v>0.25</v>
       </c>
-      <c r="AL5" s="10">
+      <c r="AL5" s="8">
         <v>140.25</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>202</v>
       </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="8"/>
-      <c r="W7" s="8"/>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="8"/>
-      <c r="Z7" s="8"/>
-      <c r="AA7" s="8"/>
-      <c r="AB7" s="8"/>
-      <c r="AC7" s="8"/>
-      <c r="AD7" s="8"/>
-      <c r="AE7" s="8"/>
-      <c r="AF7" s="8"/>
-      <c r="AG7" s="8"/>
-      <c r="AH7" s="8"/>
-      <c r="AI7" s="8"/>
-      <c r="AJ7" s="8"/>
-      <c r="AK7" s="8"/>
-      <c r="AL7" s="8"/>
-    </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="B7" s="9">
+        <v>46240.67644675926</v>
+      </c>
+      <c r="C7" s="10">
+        <v>46240.67644675926</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>203</v>
       </c>
-      <c r="B8" s="8">
-        <v>46240.62467592592</v>
-      </c>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="8"/>
-      <c r="W8" s="8"/>
-      <c r="X8" s="8"/>
-      <c r="Y8" s="8"/>
-      <c r="Z8" s="8"/>
-      <c r="AA8" s="8"/>
-      <c r="AB8" s="8"/>
-      <c r="AC8" s="8"/>
-      <c r="AD8" s="8"/>
-      <c r="AE8" s="8"/>
-      <c r="AF8" s="8"/>
-      <c r="AG8" s="8"/>
-      <c r="AH8" s="8"/>
-      <c r="AI8" s="8"/>
-      <c r="AJ8" s="8"/>
-      <c r="AK8" s="8"/>
-      <c r="AL8" s="8"/>
-    </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="B8" s="9">
+        <f>NOW()</f>
+        <v>46240.67644675926</v>
+      </c>
+      <c r="C8" s="10">
+        <f>NOW()</f>
+        <v>46240.67644675926</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>204</v>
       </c>
-      <c r="B9" s="8" t="str">
-        <f>IF(NOW()&gt;B8+TIME(0,2,0),"⚠ Recalculated since Calculated-at — totals may be stale, re-run the generator script","✓ Up to date as of the Calculated-at time above")</f>
-        <v>✓ Up to date as of the Calculated-at time above</v>
-      </c>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="8"/>
-      <c r="T9" s="8"/>
-      <c r="U9" s="8"/>
-      <c r="V9" s="8"/>
-      <c r="W9" s="8"/>
-      <c r="X9" s="8"/>
-      <c r="Y9" s="8"/>
-      <c r="Z9" s="8"/>
-      <c r="AA9" s="8"/>
-      <c r="AB9" s="8"/>
-      <c r="AC9" s="8"/>
-      <c r="AD9" s="8"/>
-      <c r="AE9" s="8"/>
-      <c r="AF9" s="8"/>
-      <c r="AG9" s="8"/>
-      <c r="AH9" s="8"/>
-      <c r="AI9" s="8"/>
-      <c r="AJ9" s="8"/>
-      <c r="AK9" s="8"/>
-      <c r="AL9" s="8"/>
+      <c r="B9" t="str">
+        <f>IF(C8&gt;C7+TIME(0,0,15),"⚠ Recalculated since Saved — totals may be stale, re-run the generator script","✓ Up to date as of Saved")</f>
+        <v>✓ Up to date as of Saved</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>205</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/content/backtrack2abq/data/dance-schedule.xlsx
+++ b/content/backtrack2abq/data/dance-schedule.xlsx
@@ -2357,10 +2357,10 @@
         <v>202</v>
       </c>
       <c r="B7" s="9">
-        <v>46240.67644675926</v>
+        <v>46245.56711805555</v>
       </c>
       <c r="C7" s="10">
-        <v>46240.67644675926</v>
+        <v>46245.56711805555</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2369,11 +2369,11 @@
       </c>
       <c r="B8" s="9">
         <f>NOW()</f>
-        <v>46240.67644675926</v>
+        <v>46245.56711805555</v>
       </c>
       <c r="C8" s="10">
         <f>NOW()</f>
-        <v>46240.67644675926</v>
+        <v>46245.56711805555</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -3022,10 +3022,10 @@
         <v>202</v>
       </c>
       <c r="B7" s="9">
-        <v>46240.67644675926</v>
+        <v>46245.56711805555</v>
       </c>
       <c r="C7" s="10">
-        <v>46240.67644675926</v>
+        <v>46245.56711805555</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -3034,11 +3034,11 @@
       </c>
       <c r="B8" s="9">
         <f>NOW()</f>
-        <v>46240.67644675926</v>
+        <v>46245.56711805555</v>
       </c>
       <c r="C8" s="10">
         <f>NOW()</f>
-        <v>46240.67644675926</v>
+        <v>46245.56711805555</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">

--- a/content/backtrack2abq/data/dance-schedule.xlsx
+++ b/content/backtrack2abq/data/dance-schedule.xlsx
@@ -10,15 +10,13 @@
     <sheet sheetId="1" name="Thursday July 2" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="Friday July 3" state="visible" r:id="rId5"/>
     <sheet sheetId="3" name="Saturday July 4" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="- Hours by Level" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="- Hours by Caller" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="186">
   <si>
     <t>Time</t>
   </si>
@@ -679,181 +677,13 @@
   </si>
   <si>
     <t>5:00p-8:00p</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>SSD</t>
-  </si>
-  <si>
-    <t>Plus</t>
-  </si>
-  <si>
-    <t>A1</t>
-  </si>
-  <si>
-    <t>A2</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>C3A</t>
-  </si>
-  <si>
-    <t>C3B</t>
-  </si>
-  <si>
-    <t>C4</t>
-  </si>
-  <si>
-    <t>Intro</t>
-  </si>
-  <si>
-    <t>Various</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>Thu, Jul 2</t>
-  </si>
-  <si>
-    <t>Fri, Jul 3</t>
-  </si>
-  <si>
-    <t>Sat, Jul 4</t>
-  </si>
-  <si>
-    <t>Calculated</t>
-  </si>
-  <si>
-    <t>Saved</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Generated by scripts/generate-dance-schedule-hour-tabs.ts — re-run after editing any day's schedule.</t>
-  </si>
-  <si>
-    <t>Kris Jensen</t>
-  </si>
-  <si>
-    <t>Sandie Bryant</t>
-  </si>
-  <si>
-    <t>Ted Lizotte</t>
-  </si>
-  <si>
-    <t>Michael Kellogg</t>
-  </si>
-  <si>
-    <t>Vic Ceder</t>
-  </si>
-  <si>
-    <t>Justin Russell</t>
-  </si>
-  <si>
-    <t>Rob French</t>
-  </si>
-  <si>
-    <t>Don Moger</t>
-  </si>
-  <si>
-    <t>Barry Clasper</t>
-  </si>
-  <si>
-    <t>Dayle Hodge</t>
-  </si>
-  <si>
-    <t>Dave Hutchinson</t>
-  </si>
-  <si>
-    <t>Wendy VanderMeulen</t>
-  </si>
-  <si>
-    <t>Brian Crawford</t>
-  </si>
-  <si>
-    <t>Allan Hurst</t>
-  </si>
-  <si>
-    <t>Kurt Gollhardt</t>
-  </si>
-  <si>
-    <t>Rick Hawes</t>
-  </si>
-  <si>
-    <t>Ett McAtee</t>
-  </si>
-  <si>
-    <t>Karla Westphal</t>
-  </si>
-  <si>
-    <t>All Callers</t>
-  </si>
-  <si>
-    <t>Jenn Engimann</t>
-  </si>
-  <si>
-    <t>Marge Coahran</t>
-  </si>
-  <si>
-    <t>Terri Sherrer</t>
-  </si>
-  <si>
-    <t>Bill van Melle</t>
-  </si>
-  <si>
-    <t>Brian Jarvis</t>
-  </si>
-  <si>
-    <t>David Hartman</t>
-  </si>
-  <si>
-    <t>Jane Clewe</t>
-  </si>
-  <si>
-    <t>Janienne Alexander</t>
-  </si>
-  <si>
-    <t>John Hawley</t>
-  </si>
-  <si>
-    <t>Michael Levy</t>
-  </si>
-  <si>
-    <t>Michael Maltenfort</t>
-  </si>
-  <si>
-    <t>Patrick Aubert</t>
-  </si>
-  <si>
-    <t>Ryo Sasaki</t>
-  </si>
-  <si>
-    <t>Tim Stephens</t>
-  </si>
-  <si>
-    <t>Greg Moore</t>
-  </si>
-  <si>
-    <t>Karin Rabe</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
-  </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -886,9 +716,6 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <b/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -904,7 +731,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -927,18 +754,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="medium"/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -959,11 +779,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="19" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2136,927 +1951,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="13" width="10" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>189</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B2">
-        <v>11</v>
-      </c>
-      <c r="C2">
-        <v>7</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2">
-        <v>4</v>
-      </c>
-      <c r="F2">
-        <v>7.5</v>
-      </c>
-      <c r="G2">
-        <v>6.5</v>
-      </c>
-      <c r="H2">
-        <v>2</v>
-      </c>
-      <c r="I2">
-        <v>3</v>
-      </c>
-      <c r="J2">
-        <v>2</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B3">
-        <v>10.75</v>
-      </c>
-      <c r="C3">
-        <v>7</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>5</v>
-      </c>
-      <c r="F3">
-        <v>7</v>
-      </c>
-      <c r="G3">
-        <v>7</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-      <c r="J3">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>46.75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>201</v>
-      </c>
-      <c r="B4">
-        <v>9</v>
-      </c>
-      <c r="C4">
-        <v>10.5</v>
-      </c>
-      <c r="D4">
-        <v>2.5</v>
-      </c>
-      <c r="E4">
-        <v>6.5</v>
-      </c>
-      <c r="F4">
-        <v>5.75</v>
-      </c>
-      <c r="G4">
-        <v>5.75</v>
-      </c>
-      <c r="H4">
-        <v>2.5</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>46.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="B5" s="8">
-        <v>30.75</v>
-      </c>
-      <c r="C5" s="8">
-        <v>24.5</v>
-      </c>
-      <c r="D5" s="8">
-        <v>7.5</v>
-      </c>
-      <c r="E5" s="8">
-        <v>15.5</v>
-      </c>
-      <c r="F5" s="8">
-        <v>20.25</v>
-      </c>
-      <c r="G5" s="8">
-        <v>19.25</v>
-      </c>
-      <c r="H5" s="8">
-        <v>7.5</v>
-      </c>
-      <c r="I5" s="8">
-        <v>7</v>
-      </c>
-      <c r="J5" s="8">
-        <v>6</v>
-      </c>
-      <c r="K5" s="8">
-        <v>1</v>
-      </c>
-      <c r="L5" s="8">
-        <v>1</v>
-      </c>
-      <c r="M5" s="8">
-        <v>140.25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>202</v>
-      </c>
-      <c r="B7" s="9">
-        <v>46245.56711805555</v>
-      </c>
-      <c r="C7" s="10">
-        <v>46245.56711805555</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>203</v>
-      </c>
-      <c r="B8" s="9">
-        <f>NOW()</f>
-        <v>46245.56711805555</v>
-      </c>
-      <c r="C8" s="10">
-        <f>NOW()</f>
-        <v>46245.56711805555</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>204</v>
-      </c>
-      <c r="B9" t="str">
-        <f>IF(C8&gt;C7+TIME(0,0,15),"⚠ Recalculated since Saved — totals may be stale, re-run the generator script","✓ Up to date as of Saved")</f>
-        <v>✓ Up to date as of Saved</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>205</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL10"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="17" customWidth="1"/>
-    <col min="8" max="8" width="13" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="13" max="13" width="21" customWidth="1"/>
-    <col min="14" max="14" width="17" customWidth="1"/>
-    <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="16" width="17" customWidth="1"/>
-    <col min="17" max="18" width="13" customWidth="1"/>
-    <col min="19" max="19" width="17" customWidth="1"/>
-    <col min="20" max="20" width="10" customWidth="1"/>
-    <col min="21" max="21" width="14" customWidth="1"/>
-    <col min="22" max="24" width="16" customWidth="1"/>
-    <col min="25" max="25" width="17" customWidth="1"/>
-    <col min="26" max="26" width="15" customWidth="1"/>
-    <col min="27" max="27" width="16" customWidth="1"/>
-    <col min="28" max="28" width="13" customWidth="1"/>
-    <col min="29" max="29" width="21" customWidth="1"/>
-    <col min="30" max="30" width="14" customWidth="1"/>
-    <col min="31" max="31" width="15" customWidth="1"/>
-    <col min="32" max="32" width="21" customWidth="1"/>
-    <col min="33" max="33" width="17" customWidth="1"/>
-    <col min="34" max="34" width="13" customWidth="1"/>
-    <col min="35" max="35" width="15" customWidth="1"/>
-    <col min="36" max="37" width="13" customWidth="1"/>
-    <col min="38" max="38" width="8" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="O1" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="P1" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="R1" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="S1" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="T1" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="U1" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="V1" s="8" t="s">
-        <v>225</v>
-      </c>
-      <c r="W1" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="X1" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="Y1" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="Z1" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="AA1" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="AB1" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="AC1" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="AD1" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="AE1" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="AF1" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="AG1" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="AH1" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="AI1" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="AJ1" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="AK1" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="AL1" s="8" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B2">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>4.5</v>
-      </c>
-      <c r="F2">
-        <v>4</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
-      </c>
-      <c r="H2">
-        <v>5</v>
-      </c>
-      <c r="I2">
-        <v>5</v>
-      </c>
-      <c r="J2">
-        <v>3</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>3</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-      <c r="R2">
-        <v>1</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2">
-        <v>0</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
-      </c>
-      <c r="AF2">
-        <v>0</v>
-      </c>
-      <c r="AG2">
-        <v>0</v>
-      </c>
-      <c r="AH2">
-        <v>0</v>
-      </c>
-      <c r="AI2">
-        <v>0</v>
-      </c>
-      <c r="AJ2">
-        <v>0</v>
-      </c>
-      <c r="AK2">
-        <v>0</v>
-      </c>
-      <c r="AL2">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3">
-        <v>6</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
-        <v>4</v>
-      </c>
-      <c r="G3">
-        <v>4</v>
-      </c>
-      <c r="H3">
-        <v>4</v>
-      </c>
-      <c r="I3">
-        <v>4</v>
-      </c>
-      <c r="J3">
-        <v>3</v>
-      </c>
-      <c r="K3">
-        <v>1.5</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>1</v>
-      </c>
-      <c r="Q3">
-        <v>1</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0.5</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0.75</v>
-      </c>
-      <c r="V3">
-        <v>0.5</v>
-      </c>
-      <c r="W3">
-        <v>0.5</v>
-      </c>
-      <c r="X3" s="12">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>0</v>
-      </c>
-      <c r="Z3">
-        <v>0</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>0</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>0</v>
-      </c>
-      <c r="AK3">
-        <v>0</v>
-      </c>
-      <c r="AL3">
-        <v>46.75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>201</v>
-      </c>
-      <c r="B4">
-        <v>5</v>
-      </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>4</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="F4">
-        <v>4.5</v>
-      </c>
-      <c r="G4">
-        <v>3</v>
-      </c>
-      <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-      <c r="J4">
-        <v>3</v>
-      </c>
-      <c r="K4">
-        <v>3</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>2</v>
-      </c>
-      <c r="O4">
-        <v>1.5</v>
-      </c>
-      <c r="P4">
-        <v>0.5</v>
-      </c>
-      <c r="Q4">
-        <v>0.5</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <v>0.5</v>
-      </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <v>0</v>
-      </c>
-      <c r="X4" s="12">
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <v>0.5</v>
-      </c>
-      <c r="Z4">
-        <v>0.5</v>
-      </c>
-      <c r="AA4">
-        <v>0.5</v>
-      </c>
-      <c r="AB4">
-        <v>0.5</v>
-      </c>
-      <c r="AC4">
-        <v>0.5</v>
-      </c>
-      <c r="AD4">
-        <v>0.5</v>
-      </c>
-      <c r="AE4">
-        <v>0.5</v>
-      </c>
-      <c r="AF4">
-        <v>0.5</v>
-      </c>
-      <c r="AG4">
-        <v>0.5</v>
-      </c>
-      <c r="AH4">
-        <v>0.5</v>
-      </c>
-      <c r="AI4">
-        <v>0.5</v>
-      </c>
-      <c r="AJ4">
-        <v>0.25</v>
-      </c>
-      <c r="AK4">
-        <v>0.25</v>
-      </c>
-      <c r="AL4">
-        <v>46.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:38" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="B5" s="8">
-        <v>14</v>
-      </c>
-      <c r="C5" s="8">
-        <v>14</v>
-      </c>
-      <c r="D5" s="8">
-        <v>14</v>
-      </c>
-      <c r="E5" s="8">
-        <v>13.5</v>
-      </c>
-      <c r="F5" s="8">
-        <v>12.5</v>
-      </c>
-      <c r="G5" s="8">
-        <v>12</v>
-      </c>
-      <c r="H5" s="8">
-        <v>12</v>
-      </c>
-      <c r="I5" s="8">
-        <v>11</v>
-      </c>
-      <c r="J5" s="8">
-        <v>9</v>
-      </c>
-      <c r="K5" s="8">
-        <v>4.5</v>
-      </c>
-      <c r="L5" s="8">
-        <v>3</v>
-      </c>
-      <c r="M5" s="8">
-        <v>3</v>
-      </c>
-      <c r="N5" s="8">
-        <v>2</v>
-      </c>
-      <c r="O5" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="P5" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="R5" s="8">
-        <v>1</v>
-      </c>
-      <c r="S5" s="8">
-        <v>1</v>
-      </c>
-      <c r="T5" s="8">
-        <v>1</v>
-      </c>
-      <c r="U5" s="8">
-        <v>0.75</v>
-      </c>
-      <c r="V5" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="W5" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="X5" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="Y5" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="Z5" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="AA5" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="AB5" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="AC5" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="AD5" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="AE5" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="AF5" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="AG5" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="AH5" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="AI5" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="AJ5" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="AK5" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="AL5" s="8">
-        <v>140.25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>202</v>
-      </c>
-      <c r="B7" s="9">
-        <v>46245.56711805555</v>
-      </c>
-      <c r="C7" s="10">
-        <v>46245.56711805555</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>203</v>
-      </c>
-      <c r="B8" s="9">
-        <f>NOW()</f>
-        <v>46245.56711805555</v>
-      </c>
-      <c r="C8" s="10">
-        <f>NOW()</f>
-        <v>46245.56711805555</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>204</v>
-      </c>
-      <c r="B9" t="str">
-        <f>IF(C8&gt;C7+TIME(0,0,15),"⚠ Recalculated since Saved — totals may be stale, re-run the generator script","✓ Up to date as of Saved")</f>
-        <v>✓ Up to date as of Saved</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>205</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
 </file>